--- a/outputs/Block5B_Senate_2026_Fold_Races.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Races.xlsx
@@ -474,10 +474,10 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>3.498315625809795</v>
+        <v>3.834808259587021</v>
       </c>
       <c r="E2">
-        <v>-7.176472161128217</v>
+        <v>-8.394792308505988</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -497,10 +497,10 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>8.458498023715421</v>
+        <v>9.334793320558447</v>
       </c>
       <c r="E3">
-        <v>-1.695802107663628</v>
+        <v>-2.383298155870026</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -520,10 +520,10 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>3.203230148048448</v>
+        <v>2.620320855614978</v>
       </c>
       <c r="E4">
-        <v>-6.995912889582467</v>
+        <v>-7.364608768458694</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -543,10 +543,10 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>8.232189973614787</v>
+        <v>8.012651555086983</v>
       </c>
       <c r="E5">
-        <v>0.383899469915236</v>
+        <v>0.2041167027681823</v>
       </c>
       <c r="F5" t="s">
         <v>19</v>
@@ -566,10 +566,10 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>1.750772399588051</v>
+        <v>2.275132275132279</v>
       </c>
       <c r="E6">
-        <v>-9.075435312273683</v>
+        <v>-9.715725655312269</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -589,10 +589,10 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>1.856335754640838</v>
+        <v>2.731370989127548</v>
       </c>
       <c r="E7">
-        <v>-11.11754838992667</v>
+        <v>-9.252187445997336</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -612,10 +612,10 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>1.497081958893681</v>
+        <v>1.801573204770349</v>
       </c>
       <c r="E8">
-        <v>-8.655528146621872</v>
+        <v>-8.220303607686365</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -635,10 +635,10 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>6.065400843881861</v>
+        <v>6.331938633193857</v>
       </c>
       <c r="E9">
-        <v>-2.348561440178459</v>
+        <v>-4.659479016596833</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -658,10 +658,10 @@
         <v>18</v>
       </c>
       <c r="D10">
-        <v>-2.410596026490069</v>
+        <v>-0.7921332969134127</v>
       </c>
       <c r="E10">
-        <v>-14.69916668017758</v>
+        <v>-14.81185097149338</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -681,10 +681,10 @@
         <v>18</v>
       </c>
       <c r="D11">
-        <v>-7.215793060150304</v>
+        <v>-2.976394115430978</v>
       </c>
       <c r="E11">
-        <v>-16.77952132936703</v>
+        <v>-13.52060177460286</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -704,10 +704,10 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <v>-21.88581315216757</v>
+        <v>-24.80889506601807</v>
       </c>
       <c r="E12">
-        <v>-39.67221627274333</v>
+        <v>-44.68600897583397</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -727,10 +727,10 @@
         <v>18</v>
       </c>
       <c r="D13">
-        <v>3.498315625809795</v>
+        <v>3.834808259587021</v>
       </c>
       <c r="E13">
-        <v>3.498315625809795</v>
+        <v>3.834808259587021</v>
       </c>
       <c r="F13" t="s">
         <v>19</v>
@@ -750,10 +750,10 @@
         <v>18</v>
       </c>
       <c r="D14">
-        <v>8.458498023715421</v>
+        <v>9.334793320558447</v>
       </c>
       <c r="E14">
-        <v>8.458498023715421</v>
+        <v>9.334793320558447</v>
       </c>
       <c r="F14" t="s">
         <v>19</v>
@@ -773,10 +773,10 @@
         <v>19</v>
       </c>
       <c r="D15">
-        <v>3.203230148048448</v>
+        <v>2.620320855614978</v>
       </c>
       <c r="E15">
-        <v>3.203230148048448</v>
+        <v>2.620320855614978</v>
       </c>
       <c r="F15" t="s">
         <v>19</v>
@@ -796,10 +796,10 @@
         <v>19</v>
       </c>
       <c r="D16">
-        <v>8.232189973614787</v>
+        <v>8.012651555086983</v>
       </c>
       <c r="E16">
-        <v>8.232189973614787</v>
+        <v>8.012651555086983</v>
       </c>
       <c r="F16" t="s">
         <v>19</v>
@@ -819,10 +819,10 @@
         <v>18</v>
       </c>
       <c r="D17">
-        <v>1.750772399588051</v>
+        <v>2.275132275132279</v>
       </c>
       <c r="E17">
-        <v>1.750772399588051</v>
+        <v>2.275132275132279</v>
       </c>
       <c r="F17" t="s">
         <v>19</v>
@@ -842,10 +842,10 @@
         <v>18</v>
       </c>
       <c r="D18">
-        <v>1.856335754640838</v>
+        <v>2.731370989127548</v>
       </c>
       <c r="E18">
-        <v>1.856335754640838</v>
+        <v>2.731370989127548</v>
       </c>
       <c r="F18" t="s">
         <v>19</v>
@@ -865,10 +865,10 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>1.497081958893681</v>
+        <v>1.801573204770349</v>
       </c>
       <c r="E19">
-        <v>1.497081958893681</v>
+        <v>1.801573204770349</v>
       </c>
       <c r="F19" t="s">
         <v>19</v>
@@ -888,10 +888,10 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>6.065400843881861</v>
+        <v>6.331938633193857</v>
       </c>
       <c r="E20">
-        <v>6.065400843881861</v>
+        <v>6.331938633193857</v>
       </c>
       <c r="F20" t="s">
         <v>19</v>
@@ -911,10 +911,10 @@
         <v>18</v>
       </c>
       <c r="D21">
-        <v>-2.410596026490069</v>
+        <v>-0.7921332969134127</v>
       </c>
       <c r="E21">
-        <v>-2.410596026490069</v>
+        <v>-0.7921332969134127</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -934,10 +934,10 @@
         <v>18</v>
       </c>
       <c r="D22">
-        <v>-7.215793060150304</v>
+        <v>-2.976394115430978</v>
       </c>
       <c r="E22">
-        <v>-7.215793060150304</v>
+        <v>-2.976394115430978</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -957,10 +957,10 @@
         <v>18</v>
       </c>
       <c r="D23">
-        <v>-21.88581315216757</v>
+        <v>-24.80889506601807</v>
       </c>
       <c r="E23">
-        <v>-21.88581315216757</v>
+        <v>-24.80889506601807</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -980,10 +980,10 @@
         <v>18</v>
       </c>
       <c r="D24">
-        <v>3.498315625809795</v>
+        <v>3.834808259587021</v>
       </c>
       <c r="E24">
-        <v>2.650647024781429</v>
+        <v>1.08373866544242</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -1003,10 +1003,10 @@
         <v>18</v>
       </c>
       <c r="D25">
-        <v>8.458498023715421</v>
+        <v>9.334793320558447</v>
       </c>
       <c r="E25">
-        <v>7.738543123737648</v>
+        <v>6.648720748008175</v>
       </c>
       <c r="F25" t="s">
         <v>19</v>
@@ -1026,10 +1026,10 @@
         <v>19</v>
       </c>
       <c r="D26">
-        <v>3.203230148048448</v>
+        <v>2.620320855614978</v>
       </c>
       <c r="E26">
-        <v>5.027582767314211</v>
+        <v>4.695629952630042</v>
       </c>
       <c r="F26" t="s">
         <v>19</v>
@@ -1049,10 +1049,10 @@
         <v>19</v>
       </c>
       <c r="D27">
-        <v>8.232189973614787</v>
+        <v>8.012651555086983</v>
       </c>
       <c r="E27">
-        <v>12.31460748976793</v>
+        <v>12.10717929243599</v>
       </c>
       <c r="F27" t="s">
         <v>19</v>
@@ -1072,13 +1072,13 @@
         <v>18</v>
       </c>
       <c r="D28">
-        <v>1.750772399588051</v>
+        <v>2.275132275132279</v>
       </c>
       <c r="E28">
-        <v>0.8954172418715476</v>
+        <v>-0.04627621553369998</v>
       </c>
       <c r="F28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G28" t="s">
         <v>21</v>
@@ -1095,13 +1095,13 @@
         <v>18</v>
       </c>
       <c r="D29">
-        <v>1.856335754640838</v>
+        <v>2.731370989127548</v>
       </c>
       <c r="E29">
-        <v>-1.516711512570621</v>
+        <v>0.3743370007903817</v>
       </c>
       <c r="F29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G29" t="s">
         <v>21</v>
@@ -1118,10 +1118,10 @@
         <v>18</v>
       </c>
       <c r="D30">
-        <v>1.497081958893681</v>
+        <v>1.801573204770349</v>
       </c>
       <c r="E30">
-        <v>1.452720731242803</v>
+        <v>1.824833688550286</v>
       </c>
       <c r="F30" t="s">
         <v>19</v>
@@ -1141,10 +1141,10 @@
         <v>19</v>
       </c>
       <c r="D31">
-        <v>6.065400843881861</v>
+        <v>6.331938633193857</v>
       </c>
       <c r="E31">
-        <v>9.69704849010213</v>
+        <v>6.872988265807155</v>
       </c>
       <c r="F31" t="s">
         <v>19</v>
@@ -1164,10 +1164,10 @@
         <v>18</v>
       </c>
       <c r="D32">
-        <v>-2.410596026490069</v>
+        <v>-0.7921332969134127</v>
       </c>
       <c r="E32">
-        <v>-4.641341142383808</v>
+        <v>-5.20872947468007</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
@@ -1187,10 +1187,10 @@
         <v>18</v>
       </c>
       <c r="D33">
-        <v>-7.215793060150304</v>
+        <v>-2.976394115430978</v>
       </c>
       <c r="E33">
-        <v>-5.941181113156134</v>
+        <v>-3.187939369664107</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
@@ -1210,10 +1210,10 @@
         <v>18</v>
       </c>
       <c r="D34">
-        <v>-21.88581315216757</v>
+        <v>-24.80889506601807</v>
       </c>
       <c r="E34">
-        <v>-29.22220350797864</v>
+        <v>-34.44469546991909</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
@@ -1233,10 +1233,10 @@
         <v>18</v>
       </c>
       <c r="D35">
-        <v>3.498315625809795</v>
+        <v>3.834808259587021</v>
       </c>
       <c r="E35">
-        <v>2.032823649239744</v>
+        <v>1.221573031857961</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
@@ -1256,10 +1256,10 @@
         <v>18</v>
       </c>
       <c r="D36">
-        <v>8.458498023715421</v>
+        <v>9.334793320558447</v>
       </c>
       <c r="E36">
-        <v>6.943821333383879</v>
+        <v>6.614050023118953</v>
       </c>
       <c r="F36" t="s">
         <v>19</v>
@@ -1279,10 +1279,10 @@
         <v>19</v>
       </c>
       <c r="D37">
-        <v>3.203230148048448</v>
+        <v>2.620320855614978</v>
       </c>
       <c r="E37">
-        <v>3.313391651156564</v>
+        <v>3.097712621967635</v>
       </c>
       <c r="F37" t="s">
         <v>19</v>
@@ -1302,10 +1302,10 @@
         <v>19</v>
       </c>
       <c r="D38">
-        <v>8.232189973614787</v>
+        <v>8.012651555086983</v>
       </c>
       <c r="E38">
-        <v>9.764152809749833</v>
+        <v>9.736638244105031</v>
       </c>
       <c r="F38" t="s">
         <v>19</v>
@@ -1325,10 +1325,10 @@
         <v>18</v>
       </c>
       <c r="D39">
-        <v>1.750772399588051</v>
+        <v>2.275132275132279</v>
       </c>
       <c r="E39">
-        <v>0.328403642916468</v>
+        <v>0.00218856540450052</v>
       </c>
       <c r="F39" t="s">
         <v>19</v>
@@ -1348,13 +1348,13 @@
         <v>18</v>
       </c>
       <c r="D40">
-        <v>1.856335754640838</v>
+        <v>2.731370989127548</v>
       </c>
       <c r="E40">
-        <v>-1.309652956723542</v>
+        <v>0.4211505407111275</v>
       </c>
       <c r="F40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G40" t="s">
         <v>20</v>
@@ -1371,10 +1371,10 @@
         <v>18</v>
       </c>
       <c r="D41">
-        <v>1.497081958893681</v>
+        <v>1.801573204770349</v>
       </c>
       <c r="E41">
-        <v>0.6424537334128565</v>
+        <v>1.162823821636758</v>
       </c>
       <c r="F41" t="s">
         <v>19</v>
@@ -1394,10 +1394,10 @@
         <v>19</v>
       </c>
       <c r="D42">
-        <v>6.065400843881861</v>
+        <v>6.331938633193857</v>
       </c>
       <c r="E42">
-        <v>7.345766304429231</v>
+        <v>5.645689870519757</v>
       </c>
       <c r="F42" t="s">
         <v>19</v>
@@ -1417,10 +1417,10 @@
         <v>18</v>
       </c>
       <c r="D43">
-        <v>-2.410596026490069</v>
+        <v>-0.7921332969134127</v>
       </c>
       <c r="E43">
-        <v>-4.748170664481129</v>
+        <v>-4.454806018863352</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
@@ -1440,10 +1440,10 @@
         <v>18</v>
       </c>
       <c r="D44">
-        <v>-7.215793060150304</v>
+        <v>-2.976394115430978</v>
       </c>
       <c r="E44">
-        <v>-7.155350779947925</v>
+        <v>-3.743365246733134</v>
       </c>
       <c r="F44" t="s">
         <v>18</v>
@@ -1463,10 +1463,10 @@
         <v>18</v>
       </c>
       <c r="D45">
-        <v>-21.88581315216757</v>
+        <v>-24.80889506601807</v>
       </c>
       <c r="E45">
-        <v>-27.85683953776087</v>
+        <v>-32.20766510291654</v>
       </c>
       <c r="F45" t="s">
         <v>18</v>
@@ -1486,13 +1486,13 @@
         <v>18</v>
       </c>
       <c r="D46">
-        <v>3.498315625809795</v>
+        <v>3.834808259587021</v>
       </c>
       <c r="E46">
-        <v>0.6033611172084861</v>
+        <v>-0.6015030298294288</v>
       </c>
       <c r="F46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G46" t="s">
         <v>21</v>
@@ -1509,10 +1509,10 @@
         <v>18</v>
       </c>
       <c r="D47">
-        <v>8.458498023715421</v>
+        <v>9.334793320558447</v>
       </c>
       <c r="E47">
-        <v>6.46321041296996</v>
+        <v>5.831850282428176</v>
       </c>
       <c r="F47" t="s">
         <v>19</v>
@@ -1532,10 +1532,10 @@
         <v>19</v>
       </c>
       <c r="D48">
-        <v>3.203230148048448</v>
+        <v>2.620320855614978</v>
       </c>
       <c r="E48">
-        <v>2.413194676107785</v>
+        <v>1.947448281795106</v>
       </c>
       <c r="F48" t="s">
         <v>19</v>
@@ -1555,10 +1555,10 @@
         <v>19</v>
       </c>
       <c r="D49">
-        <v>8.232189973614787</v>
+        <v>8.012651555086983</v>
       </c>
       <c r="E49">
-        <v>10.13813397597216</v>
+        <v>9.893662163311618</v>
       </c>
       <c r="F49" t="s">
         <v>19</v>
@@ -1578,10 +1578,10 @@
         <v>18</v>
       </c>
       <c r="D50">
-        <v>1.750772399588051</v>
+        <v>2.275132275132279</v>
       </c>
       <c r="E50">
-        <v>-1.429881313643518</v>
+        <v>-2.050341687682463</v>
       </c>
       <c r="F50" t="s">
         <v>18</v>
@@ -1601,10 +1601,10 @@
         <v>18</v>
       </c>
       <c r="D51">
-        <v>1.856335754640838</v>
+        <v>2.731370989127548</v>
       </c>
       <c r="E51">
-        <v>-3.417378482927037</v>
+        <v>-1.551051621539861</v>
       </c>
       <c r="F51" t="s">
         <v>18</v>
@@ -1624,10 +1624,10 @@
         <v>18</v>
       </c>
       <c r="D52">
-        <v>1.497081958893681</v>
+        <v>1.801573204770349</v>
       </c>
       <c r="E52">
-        <v>-1.044465232996661</v>
+        <v>-0.6346464846109909</v>
       </c>
       <c r="F52" t="s">
         <v>18</v>
@@ -1647,10 +1647,10 @@
         <v>19</v>
       </c>
       <c r="D53">
-        <v>6.065400843881861</v>
+        <v>6.331938633193857</v>
       </c>
       <c r="E53">
-        <v>7.247328067624592</v>
+        <v>4.966410345570891</v>
       </c>
       <c r="F53" t="s">
         <v>19</v>
@@ -1670,10 +1670,10 @@
         <v>18</v>
       </c>
       <c r="D54">
-        <v>-2.410596026490069</v>
+        <v>-0.7921332969134127</v>
       </c>
       <c r="E54">
-        <v>-6.955336546975865</v>
+        <v>-7.214576738827462</v>
       </c>
       <c r="F54" t="s">
         <v>18</v>
@@ -1693,10 +1693,10 @@
         <v>18</v>
       </c>
       <c r="D55">
-        <v>-7.215793060150304</v>
+        <v>-2.976394115430978</v>
       </c>
       <c r="E55">
-        <v>-8.686713221810152</v>
+        <v>-5.81292646914345</v>
       </c>
       <c r="F55" t="s">
         <v>18</v>
@@ -1716,10 +1716,10 @@
         <v>18</v>
       </c>
       <c r="D56">
-        <v>-21.88581315216757</v>
+        <v>-24.80889506601807</v>
       </c>
       <c r="E56">
-        <v>-30.15733572493856</v>
+        <v>-34.92457304970939</v>
       </c>
       <c r="F56" t="s">
         <v>18</v>

--- a/outputs/Block5B_Senate_2026_Fold_Races.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Races.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="23">
   <si>
     <t>Omitted Historical Cycle</t>
   </si>
@@ -70,16 +70,19 @@
     <t>Montana</t>
   </si>
   <si>
+    <t>Kansas</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
     <t>D</t>
   </si>
   <si>
+    <t>PooledPollStructure</t>
+  </si>
+  <si>
     <t>PooledFullV11</t>
-  </si>
-  <si>
-    <t>PooledPollStructure</t>
   </si>
 </sst>
 </file>
@@ -437,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -471,19 +474,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2">
-        <v>3.834808259587021</v>
+        <v>3.348513260112512</v>
       </c>
       <c r="E2">
-        <v>-8.394792308505988</v>
+        <v>2.207651587783021</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -494,19 +497,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>9.334793320558447</v>
+        <v>8.747300215982712</v>
       </c>
       <c r="E3">
-        <v>-2.383298155870026</v>
+        <v>7.72421770476141</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -517,19 +520,19 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>2.620320855614978</v>
+        <v>3.407566407298091</v>
       </c>
       <c r="E4">
-        <v>-7.364608768458694</v>
+        <v>4.244061496758697</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -540,19 +543,19 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>8.012651555086983</v>
+        <v>8.895303070060358</v>
       </c>
       <c r="E5">
-        <v>0.2041167027681823</v>
+        <v>10.63958308823543</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -563,19 +566,19 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>2.275132275132279</v>
+        <v>1.766411811231215</v>
       </c>
       <c r="E6">
-        <v>-9.715725655312269</v>
+        <v>0.9486967156734776</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -586,19 +589,19 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>2.731370989127548</v>
+        <v>3.206997084548107</v>
       </c>
       <c r="E7">
-        <v>-9.252187445997336</v>
+        <v>2.335555605523423</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -609,19 +612,19 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>1.801573204770349</v>
+        <v>1.91115702479339</v>
       </c>
       <c r="E8">
-        <v>-8.220303607686365</v>
+        <v>1.650627714162029</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -632,19 +635,19 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9">
-        <v>6.331938633193857</v>
+        <v>7.102040816326536</v>
       </c>
       <c r="E9">
-        <v>-4.659479016596833</v>
+        <v>7.795829409818411</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -655,19 +658,19 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>-0.7921332969134127</v>
+        <v>-0.1354646437279925</v>
       </c>
       <c r="E10">
-        <v>-14.81185097149338</v>
+        <v>-1.762551866708519</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -678,19 +681,19 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11">
-        <v>-2.976394115430978</v>
+        <v>-2.941176473907625</v>
       </c>
       <c r="E11">
-        <v>-13.52060177460286</v>
+        <v>-3.055392597408815</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -701,42 +704,42 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>-24.80889506601807</v>
+        <v>-44.5744251714401</v>
       </c>
       <c r="E12">
-        <v>-44.68600897583397</v>
+        <v>-53.49871344225288</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13">
-        <v>3.834808259587021</v>
+        <v>-3.976975405546838</v>
       </c>
       <c r="E13">
-        <v>3.834808259587021</v>
+        <v>-4.597516694441605</v>
       </c>
       <c r="F13" t="s">
         <v>19</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -744,22 +747,22 @@
         <v>2010</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14">
-        <v>9.334793320558447</v>
+        <v>3.348513260112512</v>
       </c>
       <c r="E14">
-        <v>9.334793320558447</v>
+        <v>3.348513260112512</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -767,22 +770,22 @@
         <v>2010</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
       </c>
       <c r="D15">
-        <v>2.620320855614978</v>
+        <v>8.747300215982712</v>
       </c>
       <c r="E15">
-        <v>2.620320855614978</v>
+        <v>8.747300215982712</v>
       </c>
       <c r="F15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -790,22 +793,22 @@
         <v>2010</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16">
-        <v>8.012651555086983</v>
+        <v>3.407566407298091</v>
       </c>
       <c r="E16">
-        <v>8.012651555086983</v>
+        <v>3.407566407298091</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -813,22 +816,22 @@
         <v>2010</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D17">
-        <v>2.275132275132279</v>
+        <v>8.895303070060358</v>
       </c>
       <c r="E17">
-        <v>2.275132275132279</v>
+        <v>8.895303070060358</v>
       </c>
       <c r="F17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -836,22 +839,22 @@
         <v>2010</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18">
-        <v>2.731370989127548</v>
+        <v>1.766411811231215</v>
       </c>
       <c r="E18">
-        <v>2.731370989127548</v>
+        <v>1.766411811231215</v>
       </c>
       <c r="F18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -859,22 +862,22 @@
         <v>2010</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19">
-        <v>1.801573204770349</v>
+        <v>3.206997084548107</v>
       </c>
       <c r="E19">
-        <v>1.801573204770349</v>
+        <v>3.206997084548107</v>
       </c>
       <c r="F19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -882,22 +885,22 @@
         <v>2010</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
         <v>19</v>
       </c>
       <c r="D20">
-        <v>6.331938633193857</v>
+        <v>1.91115702479339</v>
       </c>
       <c r="E20">
-        <v>6.331938633193857</v>
+        <v>1.91115702479339</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -905,22 +908,22 @@
         <v>2010</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D21">
-        <v>-0.7921332969134127</v>
+        <v>7.102040816326536</v>
       </c>
       <c r="E21">
-        <v>-0.7921332969134127</v>
+        <v>7.102040816326536</v>
       </c>
       <c r="F21" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -928,22 +931,22 @@
         <v>2010</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D22">
-        <v>-2.976394115430978</v>
+        <v>-0.1354646437279925</v>
       </c>
       <c r="E22">
-        <v>-2.976394115430978</v>
+        <v>-0.1354646437279925</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -951,39 +954,39 @@
         <v>2010</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D23">
-        <v>-24.80889506601807</v>
+        <v>-2.941176473907625</v>
       </c>
       <c r="E23">
-        <v>-24.80889506601807</v>
+        <v>-2.941176473907625</v>
       </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24">
-        <v>3.834808259587021</v>
+        <v>-44.5744251714401</v>
       </c>
       <c r="E24">
-        <v>1.08373866544242</v>
+        <v>-44.5744251714401</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -994,19 +997,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D25">
-        <v>9.334793320558447</v>
+        <v>-3.976975405546838</v>
       </c>
       <c r="E25">
-        <v>6.648720748008175</v>
+        <v>-3.976975405546838</v>
       </c>
       <c r="F25" t="s">
         <v>19</v>
@@ -1020,19 +1023,19 @@
         <v>2014</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C26" t="s">
         <v>19</v>
       </c>
       <c r="D26">
-        <v>2.620320855614978</v>
+        <v>3.348513260112512</v>
       </c>
       <c r="E26">
-        <v>4.695629952630042</v>
+        <v>0.5503123267467793</v>
       </c>
       <c r="F26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G26" t="s">
         <v>21</v>
@@ -1043,19 +1046,19 @@
         <v>2014</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C27" t="s">
         <v>19</v>
       </c>
       <c r="D27">
-        <v>8.012651555086983</v>
+        <v>8.747300215982712</v>
       </c>
       <c r="E27">
-        <v>12.10717929243599</v>
+        <v>6.706792064498687</v>
       </c>
       <c r="F27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G27" t="s">
         <v>21</v>
@@ -1066,19 +1069,19 @@
         <v>2014</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D28">
-        <v>2.275132275132279</v>
+        <v>3.407566407298091</v>
       </c>
       <c r="E28">
-        <v>-0.04627621553369998</v>
+        <v>5.459894800167097</v>
       </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G28" t="s">
         <v>21</v>
@@ -1089,19 +1092,19 @@
         <v>2014</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D29">
-        <v>2.731370989127548</v>
+        <v>8.895303070060358</v>
       </c>
       <c r="E29">
-        <v>0.3743370007903817</v>
+        <v>13.44452939923259</v>
       </c>
       <c r="F29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29" t="s">
         <v>21</v>
@@ -1112,16 +1115,16 @@
         <v>2014</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D30">
-        <v>1.801573204770349</v>
+        <v>1.766411811231215</v>
       </c>
       <c r="E30">
-        <v>1.824833688550286</v>
+        <v>-0.4701608534509054</v>
       </c>
       <c r="F30" t="s">
         <v>19</v>
@@ -1135,19 +1138,19 @@
         <v>2014</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
         <v>19</v>
       </c>
       <c r="D31">
-        <v>6.331938633193857</v>
+        <v>3.206997084548107</v>
       </c>
       <c r="E31">
-        <v>6.872988265807155</v>
+        <v>0.9860233642719702</v>
       </c>
       <c r="F31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G31" t="s">
         <v>21</v>
@@ -1158,19 +1161,19 @@
         <v>2014</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D32">
-        <v>-0.7921332969134127</v>
+        <v>1.91115702479339</v>
       </c>
       <c r="E32">
-        <v>-5.20872947468007</v>
+        <v>0.9088236615002925</v>
       </c>
       <c r="F32" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G32" t="s">
         <v>21</v>
@@ -1181,19 +1184,19 @@
         <v>2014</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D33">
-        <v>-2.976394115430978</v>
+        <v>7.102040816326536</v>
       </c>
       <c r="E33">
-        <v>-3.187939369664107</v>
+        <v>9.183589830365031</v>
       </c>
       <c r="F33" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G33" t="s">
         <v>21</v>
@@ -1204,19 +1207,19 @@
         <v>2014</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D34">
-        <v>-24.80889506601807</v>
+        <v>-0.1354646437279925</v>
       </c>
       <c r="E34">
-        <v>-34.44469546991909</v>
+        <v>-4.278630805111042</v>
       </c>
       <c r="F34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G34" t="s">
         <v>21</v>
@@ -1224,71 +1227,71 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D35">
-        <v>3.834808259587021</v>
+        <v>-2.941176473907625</v>
       </c>
       <c r="E35">
-        <v>1.221573031857961</v>
+        <v>-3.142250945785637</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
       </c>
       <c r="G35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D36">
-        <v>9.334793320558447</v>
+        <v>-44.5744251714401</v>
       </c>
       <c r="E36">
-        <v>6.614050023118953</v>
+        <v>-54.7714674968241</v>
       </c>
       <c r="F36" t="s">
         <v>19</v>
       </c>
       <c r="G36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C37" t="s">
         <v>19</v>
       </c>
       <c r="D37">
-        <v>2.620320855614978</v>
+        <v>-3.976975405546838</v>
       </c>
       <c r="E37">
-        <v>3.097712621967635</v>
+        <v>-5.055886451751711</v>
       </c>
       <c r="F37" t="s">
         <v>19</v>
       </c>
       <c r="G37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1296,22 +1299,22 @@
         <v>2018</v>
       </c>
       <c r="B38" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C38" t="s">
         <v>19</v>
       </c>
       <c r="D38">
-        <v>8.012651555086983</v>
+        <v>3.348513260112512</v>
       </c>
       <c r="E38">
-        <v>9.736638244105031</v>
+        <v>2.849157985124807</v>
       </c>
       <c r="F38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G38" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1319,22 +1322,22 @@
         <v>2018</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D39">
-        <v>2.275132275132279</v>
+        <v>8.747300215982712</v>
       </c>
       <c r="E39">
-        <v>0.00218856540450052</v>
+        <v>8.21683562697547</v>
       </c>
       <c r="F39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G39" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1342,22 +1345,22 @@
         <v>2018</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D40">
-        <v>2.731370989127548</v>
+        <v>3.407566407298091</v>
       </c>
       <c r="E40">
-        <v>0.4211505407111275</v>
+        <v>5.248209899841836</v>
       </c>
       <c r="F40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1365,22 +1368,22 @@
         <v>2018</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D41">
-        <v>1.801573204770349</v>
+        <v>8.895303070060358</v>
       </c>
       <c r="E41">
-        <v>1.162823821636758</v>
+        <v>11.49108027712635</v>
       </c>
       <c r="F41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G41" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1388,22 +1391,22 @@
         <v>2018</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C42" t="s">
         <v>19</v>
       </c>
       <c r="D42">
-        <v>6.331938633193857</v>
+        <v>1.766411811231215</v>
       </c>
       <c r="E42">
-        <v>5.645689870519757</v>
+        <v>1.633240128812465</v>
       </c>
       <c r="F42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G42" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1411,22 +1414,22 @@
         <v>2018</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D43">
-        <v>-0.7921332969134127</v>
+        <v>3.206997084548107</v>
       </c>
       <c r="E43">
-        <v>-4.454806018863352</v>
+        <v>2.98051187955476</v>
       </c>
       <c r="F43" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G43" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1434,22 +1437,22 @@
         <v>2018</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D44">
-        <v>-2.976394115430978</v>
+        <v>1.91115702479339</v>
       </c>
       <c r="E44">
-        <v>-3.743365246733134</v>
+        <v>2.330258594624844</v>
       </c>
       <c r="F44" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G44" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1457,114 +1460,114 @@
         <v>2018</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D45">
-        <v>-24.80889506601807</v>
+        <v>7.102040816326536</v>
       </c>
       <c r="E45">
-        <v>-32.20766510291654</v>
+        <v>8.698462205246971</v>
       </c>
       <c r="F45" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G45" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D46">
-        <v>3.834808259587021</v>
+        <v>-0.1354646437279925</v>
       </c>
       <c r="E46">
-        <v>-0.6015030298294288</v>
+        <v>-1.017099302410275</v>
       </c>
       <c r="F46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G46" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B47" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D47">
-        <v>9.334793320558447</v>
+        <v>-2.941176473907625</v>
       </c>
       <c r="E47">
-        <v>5.831850282428176</v>
+        <v>-2.086410846675933</v>
       </c>
       <c r="F47" t="s">
         <v>19</v>
       </c>
       <c r="G47" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C48" t="s">
         <v>19</v>
       </c>
       <c r="D48">
-        <v>2.620320855614978</v>
+        <v>-44.5744251714401</v>
       </c>
       <c r="E48">
-        <v>1.947448281795106</v>
+        <v>-49.16088949307316</v>
       </c>
       <c r="F48" t="s">
         <v>19</v>
       </c>
       <c r="G48" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B49" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C49" t="s">
         <v>19</v>
       </c>
       <c r="D49">
-        <v>8.012651555086983</v>
+        <v>-3.976975405546838</v>
       </c>
       <c r="E49">
-        <v>9.893662163311618</v>
+        <v>-3.5442438966708</v>
       </c>
       <c r="F49" t="s">
         <v>19</v>
       </c>
       <c r="G49" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1572,19 +1575,19 @@
         <v>2022</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D50">
-        <v>2.275132275132279</v>
+        <v>3.348513260112512</v>
       </c>
       <c r="E50">
-        <v>-2.050341687682463</v>
+        <v>-1.205006012047791</v>
       </c>
       <c r="F50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G50" t="s">
         <v>21</v>
@@ -1595,19 +1598,19 @@
         <v>2022</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D51">
-        <v>2.731370989127548</v>
+        <v>8.747300215982712</v>
       </c>
       <c r="E51">
-        <v>-1.551051621539861</v>
+        <v>5.69148527177934</v>
       </c>
       <c r="F51" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G51" t="s">
         <v>21</v>
@@ -1618,19 +1621,19 @@
         <v>2022</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C52" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D52">
-        <v>1.801573204770349</v>
+        <v>3.407566407298091</v>
       </c>
       <c r="E52">
-        <v>-0.6346464846109909</v>
+        <v>2.841236963152701</v>
       </c>
       <c r="F52" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G52" t="s">
         <v>21</v>
@@ -1641,19 +1644,19 @@
         <v>2022</v>
       </c>
       <c r="B53" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D53">
-        <v>6.331938633193857</v>
+        <v>8.895303070060358</v>
       </c>
       <c r="E53">
-        <v>4.966410345570891</v>
+        <v>11.29841758905937</v>
       </c>
       <c r="F53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G53" t="s">
         <v>21</v>
@@ -1664,19 +1667,19 @@
         <v>2022</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C54" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D54">
-        <v>-0.7921332969134127</v>
+        <v>1.766411811231215</v>
       </c>
       <c r="E54">
-        <v>-7.214576738827462</v>
+        <v>-2.569259812284918</v>
       </c>
       <c r="F54" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G54" t="s">
         <v>21</v>
@@ -1687,19 +1690,19 @@
         <v>2022</v>
       </c>
       <c r="B55" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D55">
-        <v>-2.976394115430978</v>
+        <v>3.206997084548107</v>
       </c>
       <c r="E55">
-        <v>-5.81292646914345</v>
+        <v>-0.8853963345259084</v>
       </c>
       <c r="F55" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G55" t="s">
         <v>21</v>
@@ -1710,21 +1713,136 @@
         <v>2022</v>
       </c>
       <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56">
+        <v>1.91115702479339</v>
+      </c>
+      <c r="E56">
+        <v>-1.367040994368765</v>
+      </c>
+      <c r="F56" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>2022</v>
+      </c>
+      <c r="B57" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57">
+        <v>7.102040816326536</v>
+      </c>
+      <c r="E57">
+        <v>7.150576774776418</v>
+      </c>
+      <c r="F57" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>2022</v>
+      </c>
+      <c r="B58" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58">
+        <v>-0.1354646437279925</v>
+      </c>
+      <c r="E58">
+        <v>-6.347373519972038</v>
+      </c>
+      <c r="F58" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>2022</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59">
+        <v>-2.941176473907625</v>
+      </c>
+      <c r="E59">
+        <v>-5.769932005355074</v>
+      </c>
+      <c r="F59" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>2022</v>
+      </c>
+      <c r="B60" t="s">
         <v>17</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C60" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60">
+        <v>-44.5744251714401</v>
+      </c>
+      <c r="E60">
+        <v>-54.60026035231134</v>
+      </c>
+      <c r="F60" t="s">
+        <v>19</v>
+      </c>
+      <c r="G60" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
+        <v>2022</v>
+      </c>
+      <c r="B61" t="s">
         <v>18</v>
       </c>
-      <c r="D56">
-        <v>-24.80889506601807</v>
-      </c>
-      <c r="E56">
-        <v>-34.92457304970939</v>
-      </c>
-      <c r="F56" t="s">
-        <v>18</v>
-      </c>
-      <c r="G56" t="s">
+      <c r="C61" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61">
+        <v>-3.976975405546838</v>
+      </c>
+      <c r="E61">
+        <v>-7.512037905258658</v>
+      </c>
+      <c r="F61" t="s">
+        <v>19</v>
+      </c>
+      <c r="G61" t="s">
         <v>21</v>
       </c>
     </row>

--- a/outputs/Block5B_Senate_2026_Fold_Races.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Races.xlsx
@@ -477,10 +477,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>3.348513260112512</v>
+        <v>4.480874316939889</v>
       </c>
       <c r="E2">
-        <v>2.207651587783021</v>
+        <v>2.899996931338003</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
@@ -500,10 +500,10 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>8.747300215982712</v>
+        <v>10.0135685210312</v>
       </c>
       <c r="E3">
-        <v>7.72421770476141</v>
+        <v>8.933398731517775</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
@@ -523,10 +523,10 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>3.407566407298091</v>
+        <v>3.772582359192349</v>
       </c>
       <c r="E4">
-        <v>4.244061496758697</v>
+        <v>4.887609653950286</v>
       </c>
       <c r="F4" t="s">
         <v>20</v>
@@ -546,10 +546,10 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>8.895303070060358</v>
+        <v>8.947782734190504</v>
       </c>
       <c r="E5">
-        <v>10.63958308823543</v>
+        <v>10.69516533210181</v>
       </c>
       <c r="F5" t="s">
         <v>20</v>
@@ -569,10 +569,10 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>1.766411811231215</v>
+        <v>1.375551518297428</v>
       </c>
       <c r="E6">
-        <v>0.9486967156734776</v>
+        <v>0.9514087679052214</v>
       </c>
       <c r="F6" t="s">
         <v>20</v>
@@ -592,10 +592,10 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>3.206997084548107</v>
+        <v>2.716961223951465</v>
       </c>
       <c r="E7">
-        <v>2.335555605523423</v>
+        <v>1.941552954463196</v>
       </c>
       <c r="F7" t="s">
         <v>20</v>
@@ -615,10 +615,10 @@
         <v>19</v>
       </c>
       <c r="D8">
-        <v>1.91115702479339</v>
+        <v>2.327935222672068</v>
       </c>
       <c r="E8">
-        <v>1.650627714162029</v>
+        <v>2.647618858184431</v>
       </c>
       <c r="F8" t="s">
         <v>20</v>
@@ -638,10 +638,10 @@
         <v>20</v>
       </c>
       <c r="D9">
-        <v>7.102040816326536</v>
+        <v>7.512248230811103</v>
       </c>
       <c r="E9">
-        <v>7.795829409818411</v>
+        <v>8.223343481368309</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
@@ -661,10 +661,10 @@
         <v>19</v>
       </c>
       <c r="D10">
-        <v>-0.1354646437279925</v>
+        <v>0.507614213197968</v>
       </c>
       <c r="E10">
-        <v>-1.762551866708519</v>
+        <v>-0.7317537907371487</v>
       </c>
       <c r="F10" t="s">
         <v>19</v>
@@ -684,10 +684,10 @@
         <v>19</v>
       </c>
       <c r="D11">
-        <v>-2.941176473907625</v>
+        <v>-4.993160057968772</v>
       </c>
       <c r="E11">
-        <v>-3.055392597408815</v>
+        <v>-5.055672172429078</v>
       </c>
       <c r="F11" t="s">
         <v>19</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="D12">
-        <v>-44.5744251714401</v>
+        <v>-45.26484751203853</v>
       </c>
       <c r="E12">
-        <v>-53.49871344225288</v>
+        <v>-54.08145851217775</v>
       </c>
       <c r="F12" t="s">
         <v>19</v>
@@ -730,10 +730,10 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>-3.976975405546838</v>
+        <v>-3.663003663003671</v>
       </c>
       <c r="E13">
-        <v>-4.597516694441605</v>
+        <v>-4.291456125233902</v>
       </c>
       <c r="F13" t="s">
         <v>19</v>
@@ -753,10 +753,10 @@
         <v>19</v>
       </c>
       <c r="D14">
-        <v>3.348513260112512</v>
+        <v>4.480874316939889</v>
       </c>
       <c r="E14">
-        <v>3.348513260112512</v>
+        <v>4.480874316939889</v>
       </c>
       <c r="F14" t="s">
         <v>20</v>
@@ -776,10 +776,10 @@
         <v>19</v>
       </c>
       <c r="D15">
-        <v>8.747300215982712</v>
+        <v>10.0135685210312</v>
       </c>
       <c r="E15">
-        <v>8.747300215982712</v>
+        <v>10.0135685210312</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
@@ -799,10 +799,10 @@
         <v>20</v>
       </c>
       <c r="D16">
-        <v>3.407566407298091</v>
+        <v>3.772582359192349</v>
       </c>
       <c r="E16">
-        <v>3.407566407298091</v>
+        <v>3.772582359192349</v>
       </c>
       <c r="F16" t="s">
         <v>20</v>
@@ -822,10 +822,10 @@
         <v>20</v>
       </c>
       <c r="D17">
-        <v>8.895303070060358</v>
+        <v>8.947782734190504</v>
       </c>
       <c r="E17">
-        <v>8.895303070060358</v>
+        <v>8.947782734190504</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
@@ -845,10 +845,10 @@
         <v>19</v>
       </c>
       <c r="D18">
-        <v>1.766411811231215</v>
+        <v>1.375551518297428</v>
       </c>
       <c r="E18">
-        <v>1.766411811231215</v>
+        <v>1.375551518297428</v>
       </c>
       <c r="F18" t="s">
         <v>20</v>
@@ -868,10 +868,10 @@
         <v>19</v>
       </c>
       <c r="D19">
-        <v>3.206997084548107</v>
+        <v>2.716961223951465</v>
       </c>
       <c r="E19">
-        <v>3.206997084548107</v>
+        <v>2.716961223951465</v>
       </c>
       <c r="F19" t="s">
         <v>20</v>
@@ -891,10 +891,10 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>1.91115702479339</v>
+        <v>2.327935222672068</v>
       </c>
       <c r="E20">
-        <v>1.91115702479339</v>
+        <v>2.327935222672068</v>
       </c>
       <c r="F20" t="s">
         <v>20</v>
@@ -914,10 +914,10 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>7.102040816326536</v>
+        <v>7.512248230811103</v>
       </c>
       <c r="E21">
-        <v>7.102040816326536</v>
+        <v>7.512248230811103</v>
       </c>
       <c r="F21" t="s">
         <v>20</v>
@@ -937,13 +937,13 @@
         <v>19</v>
       </c>
       <c r="D22">
-        <v>-0.1354646437279925</v>
+        <v>0.507614213197968</v>
       </c>
       <c r="E22">
-        <v>-0.1354646437279925</v>
+        <v>0.507614213197968</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G22" t="s">
         <v>21</v>
@@ -960,10 +960,10 @@
         <v>19</v>
       </c>
       <c r="D23">
-        <v>-2.941176473907625</v>
+        <v>-4.993160057968772</v>
       </c>
       <c r="E23">
-        <v>-2.941176473907625</v>
+        <v>-4.993160057968772</v>
       </c>
       <c r="F23" t="s">
         <v>19</v>
@@ -983,10 +983,10 @@
         <v>19</v>
       </c>
       <c r="D24">
-        <v>-44.5744251714401</v>
+        <v>-45.26484751203853</v>
       </c>
       <c r="E24">
-        <v>-44.5744251714401</v>
+        <v>-45.26484751203853</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -1006,10 +1006,10 @@
         <v>19</v>
       </c>
       <c r="D25">
-        <v>-3.976975405546838</v>
+        <v>-3.663003663003671</v>
       </c>
       <c r="E25">
-        <v>-3.976975405546838</v>
+        <v>-3.663003663003671</v>
       </c>
       <c r="F25" t="s">
         <v>19</v>
@@ -1029,10 +1029,10 @@
         <v>19</v>
       </c>
       <c r="D26">
-        <v>3.348513260112512</v>
+        <v>4.480874316939889</v>
       </c>
       <c r="E26">
-        <v>0.5503123267467793</v>
+        <v>0.8233533717110268</v>
       </c>
       <c r="F26" t="s">
         <v>20</v>
@@ -1052,10 +1052,10 @@
         <v>19</v>
       </c>
       <c r="D27">
-        <v>8.747300215982712</v>
+        <v>10.0135685210312</v>
       </c>
       <c r="E27">
-        <v>6.706792064498687</v>
+        <v>7.965163214011824</v>
       </c>
       <c r="F27" t="s">
         <v>20</v>
@@ -1075,10 +1075,10 @@
         <v>20</v>
       </c>
       <c r="D28">
-        <v>3.407566407298091</v>
+        <v>3.772582359192349</v>
       </c>
       <c r="E28">
-        <v>5.459894800167097</v>
+        <v>6.46897996696539</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -1098,10 +1098,10 @@
         <v>20</v>
       </c>
       <c r="D29">
-        <v>8.895303070060358</v>
+        <v>8.947782734190504</v>
       </c>
       <c r="E29">
-        <v>13.44452939923259</v>
+        <v>13.50866379811078</v>
       </c>
       <c r="F29" t="s">
         <v>20</v>
@@ -1121,10 +1121,10 @@
         <v>19</v>
       </c>
       <c r="D30">
-        <v>1.766411811231215</v>
+        <v>1.375551518297428</v>
       </c>
       <c r="E30">
-        <v>-0.4701608534509054</v>
+        <v>-0.0348408855409188</v>
       </c>
       <c r="F30" t="s">
         <v>19</v>
@@ -1144,10 +1144,10 @@
         <v>19</v>
       </c>
       <c r="D31">
-        <v>3.206997084548107</v>
+        <v>2.716961223951465</v>
       </c>
       <c r="E31">
-        <v>0.9860233642719702</v>
+        <v>0.6610547323365017</v>
       </c>
       <c r="F31" t="s">
         <v>20</v>
@@ -1167,10 +1167,10 @@
         <v>19</v>
       </c>
       <c r="D32">
-        <v>1.91115702479339</v>
+        <v>2.327935222672068</v>
       </c>
       <c r="E32">
-        <v>0.9088236615002925</v>
+        <v>2.6354708915347</v>
       </c>
       <c r="F32" t="s">
         <v>20</v>
@@ -1190,10 +1190,10 @@
         <v>20</v>
       </c>
       <c r="D33">
-        <v>7.102040816326536</v>
+        <v>7.512248230811103</v>
       </c>
       <c r="E33">
-        <v>9.183589830365031</v>
+        <v>9.66968012404757</v>
       </c>
       <c r="F33" t="s">
         <v>20</v>
@@ -1213,10 +1213,10 @@
         <v>19</v>
       </c>
       <c r="D34">
-        <v>-0.1354646437279925</v>
+        <v>0.507614213197968</v>
       </c>
       <c r="E34">
-        <v>-4.278630805111042</v>
+        <v>-2.769332522272056</v>
       </c>
       <c r="F34" t="s">
         <v>19</v>
@@ -1236,10 +1236,10 @@
         <v>19</v>
       </c>
       <c r="D35">
-        <v>-2.941176473907625</v>
+        <v>-4.993160057968772</v>
       </c>
       <c r="E35">
-        <v>-3.142250945785637</v>
+        <v>-4.622197097031421</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
@@ -1259,10 +1259,10 @@
         <v>19</v>
       </c>
       <c r="D36">
-        <v>-44.5744251714401</v>
+        <v>-45.26484751203853</v>
       </c>
       <c r="E36">
-        <v>-54.7714674968241</v>
+        <v>-55.07160583275694</v>
       </c>
       <c r="F36" t="s">
         <v>19</v>
@@ -1282,10 +1282,10 @@
         <v>19</v>
       </c>
       <c r="D37">
-        <v>-3.976975405546838</v>
+        <v>-3.663003663003671</v>
       </c>
       <c r="E37">
-        <v>-5.055886451751711</v>
+        <v>-4.829441525200657</v>
       </c>
       <c r="F37" t="s">
         <v>19</v>
@@ -1305,10 +1305,10 @@
         <v>19</v>
       </c>
       <c r="D38">
-        <v>3.348513260112512</v>
+        <v>4.480874316939889</v>
       </c>
       <c r="E38">
-        <v>2.849157985124807</v>
+        <v>3.509269780851924</v>
       </c>
       <c r="F38" t="s">
         <v>20</v>
@@ -1328,10 +1328,10 @@
         <v>19</v>
       </c>
       <c r="D39">
-        <v>8.747300215982712</v>
+        <v>10.0135685210312</v>
       </c>
       <c r="E39">
-        <v>8.21683562697547</v>
+        <v>9.389458666446464</v>
       </c>
       <c r="F39" t="s">
         <v>20</v>
@@ -1351,10 +1351,10 @@
         <v>20</v>
       </c>
       <c r="D40">
-        <v>3.407566407298091</v>
+        <v>3.772582359192349</v>
       </c>
       <c r="E40">
-        <v>5.248209899841836</v>
+        <v>5.879464493260798</v>
       </c>
       <c r="F40" t="s">
         <v>20</v>
@@ -1374,10 +1374,10 @@
         <v>20</v>
       </c>
       <c r="D41">
-        <v>8.895303070060358</v>
+        <v>8.947782734190504</v>
       </c>
       <c r="E41">
-        <v>11.49108027712635</v>
+        <v>11.54343452574977</v>
       </c>
       <c r="F41" t="s">
         <v>20</v>
@@ -1397,10 +1397,10 @@
         <v>19</v>
       </c>
       <c r="D42">
-        <v>1.766411811231215</v>
+        <v>1.375551518297428</v>
       </c>
       <c r="E42">
-        <v>1.633240128812465</v>
+        <v>1.644285686526526</v>
       </c>
       <c r="F42" t="s">
         <v>20</v>
@@ -1420,10 +1420,10 @@
         <v>19</v>
       </c>
       <c r="D43">
-        <v>3.206997084548107</v>
+        <v>2.716961223951465</v>
       </c>
       <c r="E43">
-        <v>2.98051187955476</v>
+        <v>2.598068690669292</v>
       </c>
       <c r="F43" t="s">
         <v>20</v>
@@ -1443,10 +1443,10 @@
         <v>19</v>
       </c>
       <c r="D44">
-        <v>1.91115702479339</v>
+        <v>2.327935222672068</v>
       </c>
       <c r="E44">
-        <v>2.330258594624844</v>
+        <v>3.313029187313943</v>
       </c>
       <c r="F44" t="s">
         <v>20</v>
@@ -1466,10 +1466,10 @@
         <v>20</v>
       </c>
       <c r="D45">
-        <v>7.102040816326536</v>
+        <v>7.512248230811103</v>
       </c>
       <c r="E45">
-        <v>8.698462205246971</v>
+        <v>9.112872181436403</v>
       </c>
       <c r="F45" t="s">
         <v>20</v>
@@ -1489,10 +1489,10 @@
         <v>19</v>
       </c>
       <c r="D46">
-        <v>-0.1354646437279925</v>
+        <v>0.507614213197968</v>
       </c>
       <c r="E46">
-        <v>-1.017099302410275</v>
+        <v>-0.01361743863398268</v>
       </c>
       <c r="F46" t="s">
         <v>19</v>
@@ -1512,10 +1512,10 @@
         <v>19</v>
       </c>
       <c r="D47">
-        <v>-2.941176473907625</v>
+        <v>-4.993160057968772</v>
       </c>
       <c r="E47">
-        <v>-2.086410846675933</v>
+        <v>-3.923234843247019</v>
       </c>
       <c r="F47" t="s">
         <v>19</v>
@@ -1535,10 +1535,10 @@
         <v>19</v>
       </c>
       <c r="D48">
-        <v>-44.5744251714401</v>
+        <v>-45.26484751203853</v>
       </c>
       <c r="E48">
-        <v>-49.16088949307316</v>
+        <v>-49.68996678266883</v>
       </c>
       <c r="F48" t="s">
         <v>19</v>
@@ -1558,10 +1558,10 @@
         <v>19</v>
       </c>
       <c r="D49">
-        <v>-3.976975405546838</v>
+        <v>-3.663003663003671</v>
       </c>
       <c r="E49">
-        <v>-3.5442438966708</v>
+        <v>-3.265242901320678</v>
       </c>
       <c r="F49" t="s">
         <v>19</v>
@@ -1581,10 +1581,10 @@
         <v>19</v>
       </c>
       <c r="D50">
-        <v>3.348513260112512</v>
+        <v>4.480874316939889</v>
       </c>
       <c r="E50">
-        <v>-1.205006012047791</v>
+        <v>-0.6118390830274762</v>
       </c>
       <c r="F50" t="s">
         <v>19</v>
@@ -1604,10 +1604,10 @@
         <v>19</v>
       </c>
       <c r="D51">
-        <v>8.747300215982712</v>
+        <v>10.0135685210312</v>
       </c>
       <c r="E51">
-        <v>5.69148527177934</v>
+        <v>7.153485216836731</v>
       </c>
       <c r="F51" t="s">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         <v>20</v>
       </c>
       <c r="D52">
-        <v>3.407566407298091</v>
+        <v>3.772582359192349</v>
       </c>
       <c r="E52">
-        <v>2.841236963152701</v>
+        <v>3.804338991708963</v>
       </c>
       <c r="F52" t="s">
         <v>20</v>
@@ -1650,10 +1650,10 @@
         <v>20</v>
       </c>
       <c r="D53">
-        <v>8.895303070060358</v>
+        <v>8.947782734190504</v>
       </c>
       <c r="E53">
-        <v>11.29841758905937</v>
+        <v>11.36905065506951</v>
       </c>
       <c r="F53" t="s">
         <v>20</v>
@@ -1673,10 +1673,10 @@
         <v>19</v>
       </c>
       <c r="D54">
-        <v>1.766411811231215</v>
+        <v>1.375551518297428</v>
       </c>
       <c r="E54">
-        <v>-2.569259812284918</v>
+        <v>-2.330206567847096</v>
       </c>
       <c r="F54" t="s">
         <v>19</v>
@@ -1696,10 +1696,10 @@
         <v>19</v>
       </c>
       <c r="D55">
-        <v>3.206997084548107</v>
+        <v>2.716961223951465</v>
       </c>
       <c r="E55">
-        <v>-0.8853963345259084</v>
+        <v>-1.315406838751676</v>
       </c>
       <c r="F55" t="s">
         <v>19</v>
@@ -1719,13 +1719,13 @@
         <v>19</v>
       </c>
       <c r="D56">
-        <v>1.91115702479339</v>
+        <v>2.327935222672068</v>
       </c>
       <c r="E56">
-        <v>-1.367040994368765</v>
+        <v>0.2140625270838568</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G56" t="s">
         <v>21</v>
@@ -1742,10 +1742,10 @@
         <v>20</v>
       </c>
       <c r="D57">
-        <v>7.102040816326536</v>
+        <v>7.512248230811103</v>
       </c>
       <c r="E57">
-        <v>7.150576774776418</v>
+        <v>7.689928342794511</v>
       </c>
       <c r="F57" t="s">
         <v>20</v>
@@ -1765,10 +1765,10 @@
         <v>19</v>
       </c>
       <c r="D58">
-        <v>-0.1354646437279925</v>
+        <v>0.507614213197968</v>
       </c>
       <c r="E58">
-        <v>-6.347373519972038</v>
+        <v>-4.901089640803971</v>
       </c>
       <c r="F58" t="s">
         <v>19</v>
@@ -1788,10 +1788,10 @@
         <v>19</v>
       </c>
       <c r="D59">
-        <v>-2.941176473907625</v>
+        <v>-4.993160057968772</v>
       </c>
       <c r="E59">
-        <v>-5.769932005355074</v>
+        <v>-7.284368204258474</v>
       </c>
       <c r="F59" t="s">
         <v>19</v>
@@ -1811,10 +1811,10 @@
         <v>19</v>
       </c>
       <c r="D60">
-        <v>-44.5744251714401</v>
+        <v>-45.26484751203853</v>
       </c>
       <c r="E60">
-        <v>-54.60026035231134</v>
+        <v>-54.9440409726426</v>
       </c>
       <c r="F60" t="s">
         <v>19</v>
@@ -1834,10 +1834,10 @@
         <v>19</v>
       </c>
       <c r="D61">
-        <v>-3.976975405546838</v>
+        <v>-3.663003663003671</v>
       </c>
       <c r="E61">
-        <v>-7.512037905258658</v>
+        <v>-7.280315694596965</v>
       </c>
       <c r="F61" t="s">
         <v>19</v>

--- a/outputs/Block5B_Senate_2026_Fold_Races.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Races.xlsx
@@ -477,10 +477,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>4.480874316939889</v>
+        <v>4.506965310024583</v>
       </c>
       <c r="E2">
-        <v>2.899996931338003</v>
+        <v>2.934575079507524</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
@@ -500,10 +500,10 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>10.0135685210312</v>
+        <v>10.17639077340569</v>
       </c>
       <c r="E3">
-        <v>8.933398731517775</v>
+        <v>9.105846979584094</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
@@ -523,10 +523,10 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>3.772582359192349</v>
+        <v>3.918954945347906</v>
       </c>
       <c r="E4">
-        <v>4.887609653950286</v>
+        <v>4.952355098335075</v>
       </c>
       <c r="F4" t="s">
         <v>20</v>
@@ -546,10 +546,10 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>8.947782734190504</v>
+        <v>9.156939040207519</v>
       </c>
       <c r="E5">
-        <v>10.69516533210181</v>
+        <v>11.2222521263145</v>
       </c>
       <c r="F5" t="s">
         <v>20</v>
@@ -569,10 +569,10 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>1.375551518297428</v>
+        <v>1.348547717842322</v>
       </c>
       <c r="E6">
-        <v>0.9514087679052214</v>
+        <v>0.9436425056113893</v>
       </c>
       <c r="F6" t="s">
         <v>20</v>
@@ -592,10 +592,10 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>2.716961223951465</v>
+        <v>2.866158296082041</v>
       </c>
       <c r="E7">
-        <v>1.941552954463196</v>
+        <v>2.182906480618617</v>
       </c>
       <c r="F7" t="s">
         <v>20</v>
@@ -615,10 +615,10 @@
         <v>19</v>
       </c>
       <c r="D8">
-        <v>2.327935222672068</v>
+        <v>2.805194805194802</v>
       </c>
       <c r="E8">
-        <v>2.647618858184431</v>
+        <v>2.444738081797682</v>
       </c>
       <c r="F8" t="s">
         <v>20</v>
@@ -638,10 +638,10 @@
         <v>20</v>
       </c>
       <c r="D9">
-        <v>7.512248230811103</v>
+        <v>7.043010752688183</v>
       </c>
       <c r="E9">
-        <v>8.223343481368309</v>
+        <v>8.045819412749589</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
@@ -661,10 +661,10 @@
         <v>19</v>
       </c>
       <c r="D10">
-        <v>0.507614213197968</v>
+        <v>0.5601493731661762</v>
       </c>
       <c r="E10">
-        <v>-0.7317537907371487</v>
+        <v>-0.6344447829808589</v>
       </c>
       <c r="F10" t="s">
         <v>19</v>
@@ -684,10 +684,10 @@
         <v>19</v>
       </c>
       <c r="D11">
-        <v>-4.993160057968772</v>
+        <v>-5.37855430626928</v>
       </c>
       <c r="E11">
-        <v>-5.055672172429078</v>
+        <v>-5.47765337273122</v>
       </c>
       <c r="F11" t="s">
         <v>19</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="D12">
-        <v>-45.26484751203853</v>
+        <v>-45.28680304853589</v>
       </c>
       <c r="E12">
-        <v>-54.08145851217775</v>
+        <v>-54.09591616858408</v>
       </c>
       <c r="F12" t="s">
         <v>19</v>
@@ -730,10 +730,10 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>-3.663003663003671</v>
+        <v>-1.263101316850296</v>
       </c>
       <c r="E13">
-        <v>-4.291456125233902</v>
+        <v>-2.653435444606227</v>
       </c>
       <c r="F13" t="s">
         <v>19</v>
@@ -753,10 +753,10 @@
         <v>19</v>
       </c>
       <c r="D14">
-        <v>4.480874316939889</v>
+        <v>4.506965310024583</v>
       </c>
       <c r="E14">
-        <v>4.480874316939889</v>
+        <v>4.506965310024583</v>
       </c>
       <c r="F14" t="s">
         <v>20</v>
@@ -776,10 +776,10 @@
         <v>19</v>
       </c>
       <c r="D15">
-        <v>10.0135685210312</v>
+        <v>10.17639077340569</v>
       </c>
       <c r="E15">
-        <v>10.0135685210312</v>
+        <v>10.17639077340569</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
@@ -799,10 +799,10 @@
         <v>20</v>
       </c>
       <c r="D16">
-        <v>3.772582359192349</v>
+        <v>3.918954945347906</v>
       </c>
       <c r="E16">
-        <v>3.772582359192349</v>
+        <v>3.918954945347906</v>
       </c>
       <c r="F16" t="s">
         <v>20</v>
@@ -822,10 +822,10 @@
         <v>20</v>
       </c>
       <c r="D17">
-        <v>8.947782734190504</v>
+        <v>9.156939040207519</v>
       </c>
       <c r="E17">
-        <v>8.947782734190504</v>
+        <v>9.156939040207519</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
@@ -845,10 +845,10 @@
         <v>19</v>
       </c>
       <c r="D18">
-        <v>1.375551518297428</v>
+        <v>1.348547717842322</v>
       </c>
       <c r="E18">
-        <v>1.375551518297428</v>
+        <v>1.348547717842322</v>
       </c>
       <c r="F18" t="s">
         <v>20</v>
@@ -868,10 +868,10 @@
         <v>19</v>
       </c>
       <c r="D19">
-        <v>2.716961223951465</v>
+        <v>2.866158296082041</v>
       </c>
       <c r="E19">
-        <v>2.716961223951465</v>
+        <v>2.866158296082041</v>
       </c>
       <c r="F19" t="s">
         <v>20</v>
@@ -891,10 +891,10 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>2.327935222672068</v>
+        <v>2.805194805194802</v>
       </c>
       <c r="E20">
-        <v>2.327935222672068</v>
+        <v>2.805194805194802</v>
       </c>
       <c r="F20" t="s">
         <v>20</v>
@@ -914,10 +914,10 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>7.512248230811103</v>
+        <v>7.043010752688183</v>
       </c>
       <c r="E21">
-        <v>7.512248230811103</v>
+        <v>7.043010752688183</v>
       </c>
       <c r="F21" t="s">
         <v>20</v>
@@ -937,10 +937,10 @@
         <v>19</v>
       </c>
       <c r="D22">
-        <v>0.507614213197968</v>
+        <v>0.5601493731661762</v>
       </c>
       <c r="E22">
-        <v>0.507614213197968</v>
+        <v>0.5601493731661762</v>
       </c>
       <c r="F22" t="s">
         <v>20</v>
@@ -960,10 +960,10 @@
         <v>19</v>
       </c>
       <c r="D23">
-        <v>-4.993160057968772</v>
+        <v>-5.37855430626928</v>
       </c>
       <c r="E23">
-        <v>-4.993160057968772</v>
+        <v>-5.37855430626928</v>
       </c>
       <c r="F23" t="s">
         <v>19</v>
@@ -983,10 +983,10 @@
         <v>19</v>
       </c>
       <c r="D24">
-        <v>-45.26484751203853</v>
+        <v>-45.28680304853589</v>
       </c>
       <c r="E24">
-        <v>-45.26484751203853</v>
+        <v>-45.28680304853589</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -1006,10 +1006,10 @@
         <v>19</v>
       </c>
       <c r="D25">
-        <v>-3.663003663003671</v>
+        <v>-1.263101316850296</v>
       </c>
       <c r="E25">
-        <v>-3.663003663003671</v>
+        <v>-1.263101316850296</v>
       </c>
       <c r="F25" t="s">
         <v>19</v>
@@ -1029,10 +1029,10 @@
         <v>19</v>
       </c>
       <c r="D26">
-        <v>4.480874316939889</v>
+        <v>4.506965310024583</v>
       </c>
       <c r="E26">
-        <v>0.8233533717110268</v>
+        <v>0.8704550594324671</v>
       </c>
       <c r="F26" t="s">
         <v>20</v>
@@ -1052,10 +1052,10 @@
         <v>19</v>
       </c>
       <c r="D27">
-        <v>10.0135685210312</v>
+        <v>10.17639077340569</v>
       </c>
       <c r="E27">
-        <v>7.965163214011824</v>
+        <v>8.164145190232837</v>
       </c>
       <c r="F27" t="s">
         <v>20</v>
@@ -1075,10 +1075,10 @@
         <v>20</v>
       </c>
       <c r="D28">
-        <v>3.772582359192349</v>
+        <v>3.918954945347906</v>
       </c>
       <c r="E28">
-        <v>6.46897996696539</v>
+        <v>6.450046158743803</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -1098,10 +1098,10 @@
         <v>20</v>
       </c>
       <c r="D29">
-        <v>8.947782734190504</v>
+        <v>9.156939040207519</v>
       </c>
       <c r="E29">
-        <v>13.50866379811078</v>
+        <v>14.43379052856994</v>
       </c>
       <c r="F29" t="s">
         <v>20</v>
@@ -1121,10 +1121,10 @@
         <v>19</v>
       </c>
       <c r="D30">
-        <v>1.375551518297428</v>
+        <v>1.348547717842322</v>
       </c>
       <c r="E30">
-        <v>-0.0348408855409188</v>
+        <v>-0.02219257150778509</v>
       </c>
       <c r="F30" t="s">
         <v>19</v>
@@ -1144,10 +1144,10 @@
         <v>19</v>
       </c>
       <c r="D31">
-        <v>2.716961223951465</v>
+        <v>2.866158296082041</v>
       </c>
       <c r="E31">
-        <v>0.6610547323365017</v>
+        <v>1.025982213875479</v>
       </c>
       <c r="F31" t="s">
         <v>20</v>
@@ -1167,10 +1167,10 @@
         <v>19</v>
       </c>
       <c r="D32">
-        <v>2.327935222672068</v>
+        <v>2.805194805194802</v>
       </c>
       <c r="E32">
-        <v>2.6354708915347</v>
+        <v>1.666649825452963</v>
       </c>
       <c r="F32" t="s">
         <v>20</v>
@@ -1190,10 +1190,10 @@
         <v>20</v>
       </c>
       <c r="D33">
-        <v>7.512248230811103</v>
+        <v>7.043010752688183</v>
       </c>
       <c r="E33">
-        <v>9.66968012404757</v>
+        <v>9.796187483455562</v>
       </c>
       <c r="F33" t="s">
         <v>20</v>
@@ -1213,10 +1213,10 @@
         <v>19</v>
       </c>
       <c r="D34">
-        <v>0.507614213197968</v>
+        <v>0.5601493731661762</v>
       </c>
       <c r="E34">
-        <v>-2.769332522272056</v>
+        <v>-2.613832013578531</v>
       </c>
       <c r="F34" t="s">
         <v>19</v>
@@ -1236,10 +1236,10 @@
         <v>19</v>
       </c>
       <c r="D35">
-        <v>-4.993160057968772</v>
+        <v>-5.37855430626928</v>
       </c>
       <c r="E35">
-        <v>-4.622197097031421</v>
+        <v>-5.001596415461596</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
@@ -1259,10 +1259,10 @@
         <v>19</v>
       </c>
       <c r="D36">
-        <v>-45.26484751203853</v>
+        <v>-45.28680304853589</v>
       </c>
       <c r="E36">
-        <v>-55.07160583275694</v>
+        <v>-55.07222437890977</v>
       </c>
       <c r="F36" t="s">
         <v>19</v>
@@ -1282,10 +1282,10 @@
         <v>19</v>
       </c>
       <c r="D37">
-        <v>-3.663003663003671</v>
+        <v>-1.263101316850296</v>
       </c>
       <c r="E37">
-        <v>-4.829441525200657</v>
+        <v>-4.635421475606936</v>
       </c>
       <c r="F37" t="s">
         <v>19</v>
@@ -1305,10 +1305,10 @@
         <v>19</v>
       </c>
       <c r="D38">
-        <v>4.480874316939889</v>
+        <v>4.506965310024583</v>
       </c>
       <c r="E38">
-        <v>3.509269780851924</v>
+        <v>3.512520306995779</v>
       </c>
       <c r="F38" t="s">
         <v>20</v>
@@ -1328,10 +1328,10 @@
         <v>19</v>
       </c>
       <c r="D39">
-        <v>10.0135685210312</v>
+        <v>10.17639077340569</v>
       </c>
       <c r="E39">
-        <v>9.389458666446464</v>
+        <v>9.526811563995569</v>
       </c>
       <c r="F39" t="s">
         <v>20</v>
@@ -1351,10 +1351,10 @@
         <v>20</v>
       </c>
       <c r="D40">
-        <v>3.772582359192349</v>
+        <v>3.918954945347906</v>
       </c>
       <c r="E40">
-        <v>5.879464493260798</v>
+        <v>5.909719293868223</v>
       </c>
       <c r="F40" t="s">
         <v>20</v>
@@ -1374,10 +1374,10 @@
         <v>20</v>
       </c>
       <c r="D41">
-        <v>8.947782734190504</v>
+        <v>9.156939040207519</v>
       </c>
       <c r="E41">
-        <v>11.54343452574977</v>
+        <v>12.03363747660556</v>
       </c>
       <c r="F41" t="s">
         <v>20</v>
@@ -1397,10 +1397,10 @@
         <v>19</v>
       </c>
       <c r="D42">
-        <v>1.375551518297428</v>
+        <v>1.348547717842322</v>
       </c>
       <c r="E42">
-        <v>1.644285686526526</v>
+        <v>1.6066362667385</v>
       </c>
       <c r="F42" t="s">
         <v>20</v>
@@ -1420,10 +1420,10 @@
         <v>19</v>
       </c>
       <c r="D43">
-        <v>2.716961223951465</v>
+        <v>2.866158296082041</v>
       </c>
       <c r="E43">
-        <v>2.598068690669292</v>
+        <v>2.804564973435884</v>
       </c>
       <c r="F43" t="s">
         <v>20</v>
@@ -1443,10 +1443,10 @@
         <v>19</v>
       </c>
       <c r="D44">
-        <v>2.327935222672068</v>
+        <v>2.805194805194802</v>
       </c>
       <c r="E44">
-        <v>3.313029187313943</v>
+        <v>3.067539176143721</v>
       </c>
       <c r="F44" t="s">
         <v>20</v>
@@ -1466,10 +1466,10 @@
         <v>20</v>
       </c>
       <c r="D45">
-        <v>7.512248230811103</v>
+        <v>7.043010752688183</v>
       </c>
       <c r="E45">
-        <v>9.112872181436403</v>
+        <v>8.917192079051359</v>
       </c>
       <c r="F45" t="s">
         <v>20</v>
@@ -1489,13 +1489,13 @@
         <v>19</v>
       </c>
       <c r="D46">
-        <v>0.507614213197968</v>
+        <v>0.5601493731661762</v>
       </c>
       <c r="E46">
-        <v>-0.01361743863398268</v>
+        <v>0.051575320809509</v>
       </c>
       <c r="F46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G46" t="s">
         <v>22</v>
@@ -1512,10 +1512,10 @@
         <v>19</v>
       </c>
       <c r="D47">
-        <v>-4.993160057968772</v>
+        <v>-5.37855430626928</v>
       </c>
       <c r="E47">
-        <v>-3.923234843247019</v>
+        <v>-4.344700706520976</v>
       </c>
       <c r="F47" t="s">
         <v>19</v>
@@ -1535,10 +1535,10 @@
         <v>19</v>
       </c>
       <c r="D48">
-        <v>-45.26484751203853</v>
+        <v>-45.28680304853589</v>
       </c>
       <c r="E48">
-        <v>-49.68996678266883</v>
+        <v>-49.73326296465212</v>
       </c>
       <c r="F48" t="s">
         <v>19</v>
@@ -1558,10 +1558,10 @@
         <v>19</v>
       </c>
       <c r="D49">
-        <v>-3.663003663003671</v>
+        <v>-1.263101316850296</v>
       </c>
       <c r="E49">
-        <v>-3.265242901320678</v>
+        <v>-1.849900167308826</v>
       </c>
       <c r="F49" t="s">
         <v>19</v>
@@ -1581,10 +1581,10 @@
         <v>19</v>
       </c>
       <c r="D50">
-        <v>4.480874316939889</v>
+        <v>4.506965310024583</v>
       </c>
       <c r="E50">
-        <v>-0.6118390830274762</v>
+        <v>-0.5639709206460912</v>
       </c>
       <c r="F50" t="s">
         <v>19</v>
@@ -1604,10 +1604,10 @@
         <v>19</v>
       </c>
       <c r="D51">
-        <v>10.0135685210312</v>
+        <v>10.17639077340569</v>
       </c>
       <c r="E51">
-        <v>7.153485216836731</v>
+        <v>7.372629814854099</v>
       </c>
       <c r="F51" t="s">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         <v>20</v>
       </c>
       <c r="D52">
-        <v>3.772582359192349</v>
+        <v>3.918954945347906</v>
       </c>
       <c r="E52">
-        <v>3.804338991708963</v>
+        <v>3.835568370743952</v>
       </c>
       <c r="F52" t="s">
         <v>20</v>
@@ -1650,10 +1650,10 @@
         <v>20</v>
       </c>
       <c r="D53">
-        <v>8.947782734190504</v>
+        <v>9.156939040207519</v>
       </c>
       <c r="E53">
-        <v>11.36905065506951</v>
+        <v>12.21164282465422</v>
       </c>
       <c r="F53" t="s">
         <v>20</v>
@@ -1673,10 +1673,10 @@
         <v>19</v>
       </c>
       <c r="D54">
-        <v>1.375551518297428</v>
+        <v>1.348547717842322</v>
       </c>
       <c r="E54">
-        <v>-2.330206567847096</v>
+        <v>-2.328295474778286</v>
       </c>
       <c r="F54" t="s">
         <v>19</v>
@@ -1696,10 +1696,10 @@
         <v>19</v>
       </c>
       <c r="D55">
-        <v>2.716961223951465</v>
+        <v>2.866158296082041</v>
       </c>
       <c r="E55">
-        <v>-1.315406838751676</v>
+        <v>-0.9615771044751797</v>
       </c>
       <c r="F55" t="s">
         <v>19</v>
@@ -1719,13 +1719,13 @@
         <v>19</v>
       </c>
       <c r="D56">
-        <v>2.327935222672068</v>
+        <v>2.805194805194802</v>
       </c>
       <c r="E56">
-        <v>0.2140625270838568</v>
+        <v>-0.4442868396550299</v>
       </c>
       <c r="F56" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G56" t="s">
         <v>21</v>
@@ -1742,10 +1742,10 @@
         <v>20</v>
       </c>
       <c r="D57">
-        <v>7.512248230811103</v>
+        <v>7.043010752688183</v>
       </c>
       <c r="E57">
-        <v>7.689928342794511</v>
+        <v>7.644965357194693</v>
       </c>
       <c r="F57" t="s">
         <v>20</v>
@@ -1765,10 +1765,10 @@
         <v>19</v>
       </c>
       <c r="D58">
-        <v>0.507614213197968</v>
+        <v>0.5601493731661762</v>
       </c>
       <c r="E58">
-        <v>-4.901089640803971</v>
+        <v>-4.753870159985402</v>
       </c>
       <c r="F58" t="s">
         <v>19</v>
@@ -1788,10 +1788,10 @@
         <v>19</v>
       </c>
       <c r="D59">
-        <v>-4.993160057968772</v>
+        <v>-5.37855430626928</v>
       </c>
       <c r="E59">
-        <v>-7.284368204258474</v>
+        <v>-7.65381576757183</v>
       </c>
       <c r="F59" t="s">
         <v>19</v>
@@ -1811,10 +1811,10 @@
         <v>19</v>
       </c>
       <c r="D60">
-        <v>-45.26484751203853</v>
+        <v>-45.28680304853589</v>
       </c>
       <c r="E60">
-        <v>-54.9440409726426</v>
+        <v>-54.94749297860604</v>
       </c>
       <c r="F60" t="s">
         <v>19</v>
@@ -1834,10 +1834,10 @@
         <v>19</v>
       </c>
       <c r="D61">
-        <v>-3.663003663003671</v>
+        <v>-1.263101316850296</v>
       </c>
       <c r="E61">
-        <v>-7.280315694596965</v>
+        <v>-6.797050512559895</v>
       </c>
       <c r="F61" t="s">
         <v>19</v>

--- a/outputs/Block5B_Senate_2026_Fold_Races.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Races.xlsx
@@ -477,10 +477,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>4.506965310024583</v>
+        <v>4.35020519835841</v>
       </c>
       <c r="E2">
-        <v>2.934575079507524</v>
+        <v>2.726879376671175</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
@@ -500,10 +500,10 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>10.17639077340569</v>
+        <v>10.7103825136612</v>
       </c>
       <c r="E3">
-        <v>9.105846979584094</v>
+        <v>9.497791515143108</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
@@ -523,10 +523,10 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>3.918954945347906</v>
+        <v>3.022198448783094</v>
       </c>
       <c r="E4">
-        <v>4.952355098335075</v>
+        <v>3.919246691079949</v>
       </c>
       <c r="F4" t="s">
         <v>20</v>
@@ -569,10 +569,10 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>1.348547717842322</v>
+        <v>2.024922118380061</v>
       </c>
       <c r="E6">
-        <v>0.9436425056113893</v>
+        <v>1.63222527052263</v>
       </c>
       <c r="F6" t="s">
         <v>20</v>
@@ -592,10 +592,10 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>2.866158296082041</v>
+        <v>2.397891963109359</v>
       </c>
       <c r="E7">
-        <v>2.182906480618617</v>
+        <v>1.631399086505698</v>
       </c>
       <c r="F7" t="s">
         <v>20</v>
@@ -615,10 +615,10 @@
         <v>19</v>
       </c>
       <c r="D8">
-        <v>2.805194805194802</v>
+        <v>2.285714285714292</v>
       </c>
       <c r="E8">
-        <v>2.444738081797682</v>
+        <v>1.894546052252768</v>
       </c>
       <c r="F8" t="s">
         <v>20</v>
@@ -638,10 +638,10 @@
         <v>20</v>
       </c>
       <c r="D9">
-        <v>7.043010752688183</v>
+        <v>7.173678532901825</v>
       </c>
       <c r="E9">
-        <v>8.045819412749589</v>
+        <v>8.100876252980063</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
@@ -661,10 +661,10 @@
         <v>19</v>
       </c>
       <c r="D10">
-        <v>0.5601493731661762</v>
+        <v>-0.4870129870129816</v>
       </c>
       <c r="E10">
-        <v>-0.6344447829808589</v>
+        <v>-2.070518893146442</v>
       </c>
       <c r="F10" t="s">
         <v>19</v>
@@ -684,10 +684,10 @@
         <v>19</v>
       </c>
       <c r="D11">
-        <v>-5.37855430626928</v>
+        <v>-2.742616033755276</v>
       </c>
       <c r="E11">
-        <v>-5.47765337273122</v>
+        <v>-3.602599519005729</v>
       </c>
       <c r="F11" t="s">
         <v>19</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="D12">
-        <v>-45.28680304853589</v>
+        <v>-46.50877909350755</v>
       </c>
       <c r="E12">
-        <v>-54.09591616858408</v>
+        <v>-55.59266721589984</v>
       </c>
       <c r="F12" t="s">
         <v>19</v>
@@ -730,10 +730,10 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>-1.263101316850296</v>
+        <v>0.5161640858462349</v>
       </c>
       <c r="E13">
-        <v>-2.653435444606227</v>
+        <v>-1.153267653173353</v>
       </c>
       <c r="F13" t="s">
         <v>19</v>
@@ -753,10 +753,10 @@
         <v>19</v>
       </c>
       <c r="D14">
-        <v>4.506965310024583</v>
+        <v>4.35020519835841</v>
       </c>
       <c r="E14">
-        <v>4.506965310024583</v>
+        <v>4.35020519835841</v>
       </c>
       <c r="F14" t="s">
         <v>20</v>
@@ -776,10 +776,10 @@
         <v>19</v>
       </c>
       <c r="D15">
-        <v>10.17639077340569</v>
+        <v>10.7103825136612</v>
       </c>
       <c r="E15">
-        <v>10.17639077340569</v>
+        <v>10.7103825136612</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
@@ -799,10 +799,10 @@
         <v>20</v>
       </c>
       <c r="D16">
-        <v>3.918954945347906</v>
+        <v>3.022198448783094</v>
       </c>
       <c r="E16">
-        <v>3.918954945347906</v>
+        <v>3.022198448783094</v>
       </c>
       <c r="F16" t="s">
         <v>20</v>
@@ -845,10 +845,10 @@
         <v>19</v>
       </c>
       <c r="D18">
-        <v>1.348547717842322</v>
+        <v>2.024922118380061</v>
       </c>
       <c r="E18">
-        <v>1.348547717842322</v>
+        <v>2.024922118380061</v>
       </c>
       <c r="F18" t="s">
         <v>20</v>
@@ -868,10 +868,10 @@
         <v>19</v>
       </c>
       <c r="D19">
-        <v>2.866158296082041</v>
+        <v>2.397891963109359</v>
       </c>
       <c r="E19">
-        <v>2.866158296082041</v>
+        <v>2.397891963109359</v>
       </c>
       <c r="F19" t="s">
         <v>20</v>
@@ -891,10 +891,10 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>2.805194805194802</v>
+        <v>2.285714285714292</v>
       </c>
       <c r="E20">
-        <v>2.805194805194802</v>
+        <v>2.285714285714292</v>
       </c>
       <c r="F20" t="s">
         <v>20</v>
@@ -914,10 +914,10 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>7.043010752688183</v>
+        <v>7.173678532901825</v>
       </c>
       <c r="E21">
-        <v>7.043010752688183</v>
+        <v>7.173678532901825</v>
       </c>
       <c r="F21" t="s">
         <v>20</v>
@@ -937,13 +937,13 @@
         <v>19</v>
       </c>
       <c r="D22">
-        <v>0.5601493731661762</v>
+        <v>-0.4870129870129816</v>
       </c>
       <c r="E22">
-        <v>0.5601493731661762</v>
+        <v>-0.4870129870129816</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G22" t="s">
         <v>21</v>
@@ -960,10 +960,10 @@
         <v>19</v>
       </c>
       <c r="D23">
-        <v>-5.37855430626928</v>
+        <v>-2.742616033755276</v>
       </c>
       <c r="E23">
-        <v>-5.37855430626928</v>
+        <v>-2.742616033755276</v>
       </c>
       <c r="F23" t="s">
         <v>19</v>
@@ -983,10 +983,10 @@
         <v>19</v>
       </c>
       <c r="D24">
-        <v>-45.28680304853589</v>
+        <v>-46.50877909350755</v>
       </c>
       <c r="E24">
-        <v>-45.28680304853589</v>
+        <v>-46.50877909350755</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -1006,13 +1006,13 @@
         <v>19</v>
       </c>
       <c r="D25">
-        <v>-1.263101316850296</v>
+        <v>0.5161640858462349</v>
       </c>
       <c r="E25">
-        <v>-1.263101316850296</v>
+        <v>0.5161640858462349</v>
       </c>
       <c r="F25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G25" t="s">
         <v>21</v>
@@ -1029,10 +1029,10 @@
         <v>19</v>
       </c>
       <c r="D26">
-        <v>4.506965310024583</v>
+        <v>4.35020519835841</v>
       </c>
       <c r="E26">
-        <v>0.8704550594324671</v>
+        <v>0.5875832206046367</v>
       </c>
       <c r="F26" t="s">
         <v>20</v>
@@ -1052,10 +1052,10 @@
         <v>19</v>
       </c>
       <c r="D27">
-        <v>10.17639077340569</v>
+        <v>10.7103825136612</v>
       </c>
       <c r="E27">
-        <v>8.164145190232837</v>
+        <v>8.436316795270802</v>
       </c>
       <c r="F27" t="s">
         <v>20</v>
@@ -1075,10 +1075,10 @@
         <v>20</v>
       </c>
       <c r="D28">
-        <v>3.918954945347906</v>
+        <v>3.022198448783094</v>
       </c>
       <c r="E28">
-        <v>6.450046158743803</v>
+        <v>5.171540530193047</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -1121,13 +1121,13 @@
         <v>19</v>
       </c>
       <c r="D30">
-        <v>1.348547717842322</v>
+        <v>2.024922118380061</v>
       </c>
       <c r="E30">
-        <v>-0.02219257150778509</v>
+        <v>0.743526186134849</v>
       </c>
       <c r="F30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G30" t="s">
         <v>21</v>
@@ -1144,10 +1144,10 @@
         <v>19</v>
       </c>
       <c r="D31">
-        <v>2.866158296082041</v>
+        <v>2.397891963109359</v>
       </c>
       <c r="E31">
-        <v>1.025982213875479</v>
+        <v>0.3319917866220674</v>
       </c>
       <c r="F31" t="s">
         <v>20</v>
@@ -1167,10 +1167,10 @@
         <v>19</v>
       </c>
       <c r="D32">
-        <v>2.805194805194802</v>
+        <v>2.285714285714292</v>
       </c>
       <c r="E32">
-        <v>1.666649825452963</v>
+        <v>1.031802567985925</v>
       </c>
       <c r="F32" t="s">
         <v>20</v>
@@ -1190,10 +1190,10 @@
         <v>20</v>
       </c>
       <c r="D33">
-        <v>7.043010752688183</v>
+        <v>7.173678532901825</v>
       </c>
       <c r="E33">
-        <v>9.796187483455562</v>
+        <v>9.773277512312969</v>
       </c>
       <c r="F33" t="s">
         <v>20</v>
@@ -1213,10 +1213,10 @@
         <v>19</v>
       </c>
       <c r="D34">
-        <v>0.5601493731661762</v>
+        <v>-0.4870129870129816</v>
       </c>
       <c r="E34">
-        <v>-2.613832013578531</v>
+        <v>-4.456095086267493</v>
       </c>
       <c r="F34" t="s">
         <v>19</v>
@@ -1236,10 +1236,10 @@
         <v>19</v>
       </c>
       <c r="D35">
-        <v>-5.37855430626928</v>
+        <v>-2.742616033755276</v>
       </c>
       <c r="E35">
-        <v>-5.001596415461596</v>
+        <v>-4.622124479743986</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
@@ -1259,10 +1259,10 @@
         <v>19</v>
       </c>
       <c r="D36">
-        <v>-45.28680304853589</v>
+        <v>-46.50877909350755</v>
       </c>
       <c r="E36">
-        <v>-55.07222437890977</v>
+        <v>-56.62306739616567</v>
       </c>
       <c r="F36" t="s">
         <v>19</v>
@@ -1282,10 +1282,10 @@
         <v>19</v>
       </c>
       <c r="D37">
-        <v>-1.263101316850296</v>
+        <v>0.5161640858462349</v>
       </c>
       <c r="E37">
-        <v>-4.635421475606936</v>
+        <v>-3.702299542820164</v>
       </c>
       <c r="F37" t="s">
         <v>19</v>
@@ -1305,10 +1305,10 @@
         <v>19</v>
       </c>
       <c r="D38">
-        <v>4.506965310024583</v>
+        <v>4.35020519835841</v>
       </c>
       <c r="E38">
-        <v>3.512520306995779</v>
+        <v>3.383283553602231</v>
       </c>
       <c r="F38" t="s">
         <v>20</v>
@@ -1328,10 +1328,10 @@
         <v>19</v>
       </c>
       <c r="D39">
-        <v>10.17639077340569</v>
+        <v>10.7103825136612</v>
       </c>
       <c r="E39">
-        <v>9.526811563995569</v>
+        <v>9.978341861521631</v>
       </c>
       <c r="F39" t="s">
         <v>20</v>
@@ -1351,10 +1351,10 @@
         <v>20</v>
       </c>
       <c r="D40">
-        <v>3.918954945347906</v>
+        <v>3.022198448783094</v>
       </c>
       <c r="E40">
-        <v>5.909719293868223</v>
+        <v>4.975592679252363</v>
       </c>
       <c r="F40" t="s">
         <v>20</v>
@@ -1377,7 +1377,7 @@
         <v>9.156939040207519</v>
       </c>
       <c r="E41">
-        <v>12.03363747660556</v>
+        <v>12.107694308957</v>
       </c>
       <c r="F41" t="s">
         <v>20</v>
@@ -1397,10 +1397,10 @@
         <v>19</v>
       </c>
       <c r="D42">
-        <v>1.348547717842322</v>
+        <v>2.024922118380061</v>
       </c>
       <c r="E42">
-        <v>1.6066362667385</v>
+        <v>2.350626952871099</v>
       </c>
       <c r="F42" t="s">
         <v>20</v>
@@ -1420,10 +1420,10 @@
         <v>19</v>
       </c>
       <c r="D43">
-        <v>2.866158296082041</v>
+        <v>2.397891963109359</v>
       </c>
       <c r="E43">
-        <v>2.804564973435884</v>
+        <v>2.340149683490385</v>
       </c>
       <c r="F43" t="s">
         <v>20</v>
@@ -1443,10 +1443,10 @@
         <v>19</v>
       </c>
       <c r="D44">
-        <v>2.805194805194802</v>
+        <v>2.285714285714292</v>
       </c>
       <c r="E44">
-        <v>3.067539176143721</v>
+        <v>2.605762487767027</v>
       </c>
       <c r="F44" t="s">
         <v>20</v>
@@ -1466,10 +1466,10 @@
         <v>20</v>
       </c>
       <c r="D45">
-        <v>7.043010752688183</v>
+        <v>7.173678532901825</v>
       </c>
       <c r="E45">
-        <v>8.917192079051359</v>
+        <v>9.042832571887942</v>
       </c>
       <c r="F45" t="s">
         <v>20</v>
@@ -1489,13 +1489,13 @@
         <v>19</v>
       </c>
       <c r="D46">
-        <v>0.5601493731661762</v>
+        <v>-0.4870129870129816</v>
       </c>
       <c r="E46">
-        <v>0.051575320809509</v>
+        <v>-1.255131650404591</v>
       </c>
       <c r="F46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G46" t="s">
         <v>22</v>
@@ -1512,10 +1512,10 @@
         <v>19</v>
       </c>
       <c r="D47">
-        <v>-5.37855430626928</v>
+        <v>-2.742616033755276</v>
       </c>
       <c r="E47">
-        <v>-4.344700706520976</v>
+        <v>-2.606691039635062</v>
       </c>
       <c r="F47" t="s">
         <v>19</v>
@@ -1535,10 +1535,10 @@
         <v>19</v>
       </c>
       <c r="D48">
-        <v>-45.28680304853589</v>
+        <v>-46.50877909350755</v>
       </c>
       <c r="E48">
-        <v>-49.73326296465212</v>
+        <v>-51.05705150122986</v>
       </c>
       <c r="F48" t="s">
         <v>19</v>
@@ -1558,10 +1558,10 @@
         <v>19</v>
       </c>
       <c r="D49">
-        <v>-1.263101316850296</v>
+        <v>0.5161640858462349</v>
       </c>
       <c r="E49">
-        <v>-1.849900167308826</v>
+        <v>-0.3911901551618415</v>
       </c>
       <c r="F49" t="s">
         <v>19</v>
@@ -1581,10 +1581,10 @@
         <v>19</v>
       </c>
       <c r="D50">
-        <v>4.506965310024583</v>
+        <v>4.35020519835841</v>
       </c>
       <c r="E50">
-        <v>-0.5639709206460912</v>
+        <v>-0.8514681264693413</v>
       </c>
       <c r="F50" t="s">
         <v>19</v>
@@ -1604,10 +1604,10 @@
         <v>19</v>
       </c>
       <c r="D51">
-        <v>10.17639077340569</v>
+        <v>10.7103825136612</v>
       </c>
       <c r="E51">
-        <v>7.372629814854099</v>
+        <v>7.772537436199933</v>
       </c>
       <c r="F51" t="s">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         <v>20</v>
       </c>
       <c r="D52">
-        <v>3.918954945347906</v>
+        <v>3.022198448783094</v>
       </c>
       <c r="E52">
-        <v>3.835568370743952</v>
+        <v>2.475588634409105</v>
       </c>
       <c r="F52" t="s">
         <v>20</v>
@@ -1673,10 +1673,10 @@
         <v>19</v>
       </c>
       <c r="D54">
-        <v>1.348547717842322</v>
+        <v>2.024922118380061</v>
       </c>
       <c r="E54">
-        <v>-2.328295474778286</v>
+        <v>-1.468962141794489</v>
       </c>
       <c r="F54" t="s">
         <v>19</v>
@@ -1696,10 +1696,10 @@
         <v>19</v>
       </c>
       <c r="D55">
-        <v>2.866158296082041</v>
+        <v>2.397891963109359</v>
       </c>
       <c r="E55">
-        <v>-0.9615771044751797</v>
+        <v>-1.693838513232154</v>
       </c>
       <c r="F55" t="s">
         <v>19</v>
@@ -1719,10 +1719,10 @@
         <v>19</v>
       </c>
       <c r="D56">
-        <v>2.805194805194802</v>
+        <v>2.285714285714292</v>
       </c>
       <c r="E56">
-        <v>-0.4442868396550299</v>
+        <v>-1.143462461900912</v>
       </c>
       <c r="F56" t="s">
         <v>19</v>
@@ -1742,10 +1742,10 @@
         <v>20</v>
       </c>
       <c r="D57">
-        <v>7.043010752688183</v>
+        <v>7.173678532901825</v>
       </c>
       <c r="E57">
-        <v>7.644965357194693</v>
+        <v>7.667809386312056</v>
       </c>
       <c r="F57" t="s">
         <v>20</v>
@@ -1765,10 +1765,10 @@
         <v>19</v>
       </c>
       <c r="D58">
-        <v>0.5601493731661762</v>
+        <v>-0.4870129870129816</v>
       </c>
       <c r="E58">
-        <v>-4.753870159985402</v>
+        <v>-6.543068817687839</v>
       </c>
       <c r="F58" t="s">
         <v>19</v>
@@ -1788,10 +1788,10 @@
         <v>19</v>
       </c>
       <c r="D59">
-        <v>-5.37855430626928</v>
+        <v>-2.742616033755276</v>
       </c>
       <c r="E59">
-        <v>-7.65381576757183</v>
+        <v>-6.983595800042814</v>
       </c>
       <c r="F59" t="s">
         <v>19</v>
@@ -1811,10 +1811,10 @@
         <v>19</v>
       </c>
       <c r="D60">
-        <v>-45.28680304853589</v>
+        <v>-46.50877909350755</v>
       </c>
       <c r="E60">
-        <v>-54.94749297860604</v>
+        <v>-56.41044032645397</v>
       </c>
       <c r="F60" t="s">
         <v>19</v>
@@ -1834,10 +1834,10 @@
         <v>19</v>
       </c>
       <c r="D61">
-        <v>-1.263101316850296</v>
+        <v>0.5161640858462349</v>
       </c>
       <c r="E61">
-        <v>-6.797050512559895</v>
+        <v>-5.680203385192162</v>
       </c>
       <c r="F61" t="s">
         <v>19</v>

--- a/outputs/Block5B_Senate_2026_Fold_Races.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Races.xlsx
@@ -546,10 +546,10 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>9.156939040207519</v>
+        <v>9.290187891440489</v>
       </c>
       <c r="E5">
-        <v>11.2222521263145</v>
+        <v>11.2036513198096</v>
       </c>
       <c r="F5" t="s">
         <v>20</v>
@@ -661,10 +661,10 @@
         <v>19</v>
       </c>
       <c r="D10">
-        <v>-0.4870129870129816</v>
+        <v>0.1082837033026536</v>
       </c>
       <c r="E10">
-        <v>-2.070518893146442</v>
+        <v>-1.494981145138496</v>
       </c>
       <c r="F10" t="s">
         <v>19</v>
@@ -684,10 +684,10 @@
         <v>19</v>
       </c>
       <c r="D11">
-        <v>-2.742616033755276</v>
+        <v>-1.440922186651328</v>
       </c>
       <c r="E11">
-        <v>-3.602599519005729</v>
+        <v>-2.963354149741118</v>
       </c>
       <c r="F11" t="s">
         <v>19</v>
@@ -822,10 +822,10 @@
         <v>20</v>
       </c>
       <c r="D17">
-        <v>9.156939040207519</v>
+        <v>9.290187891440489</v>
       </c>
       <c r="E17">
-        <v>9.156939040207519</v>
+        <v>9.290187891440489</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
@@ -937,13 +937,13 @@
         <v>19</v>
       </c>
       <c r="D22">
-        <v>-0.4870129870129816</v>
+        <v>0.1082837033026536</v>
       </c>
       <c r="E22">
-        <v>-0.4870129870129816</v>
+        <v>0.1082837033026536</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G22" t="s">
         <v>21</v>
@@ -960,10 +960,10 @@
         <v>19</v>
       </c>
       <c r="D23">
-        <v>-2.742616033755276</v>
+        <v>-1.440922186651328</v>
       </c>
       <c r="E23">
-        <v>-2.742616033755276</v>
+        <v>-1.440922186651328</v>
       </c>
       <c r="F23" t="s">
         <v>19</v>
@@ -1098,10 +1098,10 @@
         <v>20</v>
       </c>
       <c r="D29">
-        <v>9.156939040207519</v>
+        <v>9.290187891440489</v>
       </c>
       <c r="E29">
-        <v>14.43379052856994</v>
+        <v>14.24665463795645</v>
       </c>
       <c r="F29" t="s">
         <v>20</v>
@@ -1213,10 +1213,10 @@
         <v>19</v>
       </c>
       <c r="D34">
-        <v>-0.4870129870129816</v>
+        <v>0.1082837033026536</v>
       </c>
       <c r="E34">
-        <v>-4.456095086267493</v>
+        <v>-4.002949436234216</v>
       </c>
       <c r="F34" t="s">
         <v>19</v>
@@ -1236,10 +1236,10 @@
         <v>19</v>
       </c>
       <c r="D35">
-        <v>-2.742616033755276</v>
+        <v>-1.440922186651328</v>
       </c>
       <c r="E35">
-        <v>-4.622124479743986</v>
+        <v>-5.062926210462702</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
@@ -1374,10 +1374,10 @@
         <v>20</v>
       </c>
       <c r="D41">
-        <v>9.156939040207519</v>
+        <v>9.290187891440489</v>
       </c>
       <c r="E41">
-        <v>12.107694308957</v>
+        <v>12.08567593496913</v>
       </c>
       <c r="F41" t="s">
         <v>20</v>
@@ -1489,10 +1489,10 @@
         <v>19</v>
       </c>
       <c r="D46">
-        <v>-0.4870129870129816</v>
+        <v>0.1082837033026536</v>
       </c>
       <c r="E46">
-        <v>-1.255131650404591</v>
+        <v>-0.7217798163800426</v>
       </c>
       <c r="F46" t="s">
         <v>19</v>
@@ -1512,10 +1512,10 @@
         <v>19</v>
       </c>
       <c r="D47">
-        <v>-2.742616033755276</v>
+        <v>-1.440922186651328</v>
       </c>
       <c r="E47">
-        <v>-2.606691039635062</v>
+        <v>-2.071216292825427</v>
       </c>
       <c r="F47" t="s">
         <v>19</v>
@@ -1650,10 +1650,10 @@
         <v>20</v>
       </c>
       <c r="D53">
-        <v>9.156939040207519</v>
+        <v>9.290187891440489</v>
       </c>
       <c r="E53">
-        <v>12.21164282465422</v>
+        <v>12.09768926023513</v>
       </c>
       <c r="F53" t="s">
         <v>20</v>
@@ -1765,10 +1765,10 @@
         <v>19</v>
       </c>
       <c r="D58">
-        <v>-0.4870129870129816</v>
+        <v>0.1082837033026536</v>
       </c>
       <c r="E58">
-        <v>-6.543068817687839</v>
+        <v>-6.063399526031018</v>
       </c>
       <c r="F58" t="s">
         <v>19</v>
@@ -1788,10 +1788,10 @@
         <v>19</v>
       </c>
       <c r="D59">
-        <v>-2.742616033755276</v>
+        <v>-1.440922186651328</v>
       </c>
       <c r="E59">
-        <v>-6.983595800042814</v>
+        <v>-7.179077005630766</v>
       </c>
       <c r="F59" t="s">
         <v>19</v>

--- a/outputs/Block5B_Senate_2026_Fold_Races.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Races.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="26">
   <si>
     <t>Omitted Historical Cycle</t>
   </si>
@@ -71,6 +71,15 @@
   </si>
   <si>
     <t>Kansas</t>
+  </si>
+  <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
   </si>
   <si>
     <t>R</t>
@@ -440,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -474,19 +483,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2">
-        <v>4.35020519835841</v>
+        <v>4.818949087939018</v>
       </c>
       <c r="E2">
-        <v>2.726879376671175</v>
+        <v>3.348339205636394</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -497,19 +506,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D3">
-        <v>10.7103825136612</v>
+        <v>11.29866594064797</v>
       </c>
       <c r="E3">
-        <v>9.497791515143108</v>
+        <v>10.21113469531803</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -520,19 +529,19 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D4">
-        <v>3.022198448783094</v>
+        <v>2.402562733582492</v>
       </c>
       <c r="E4">
-        <v>3.919246691079949</v>
+        <v>3.311590976692931</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -543,19 +552,19 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5">
-        <v>9.290187891440489</v>
+        <v>8.84210526315789</v>
       </c>
       <c r="E5">
-        <v>11.2036513198096</v>
+        <v>10.50684893545471</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -566,19 +575,19 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6">
-        <v>2.024922118380061</v>
+        <v>1.604554865424426</v>
       </c>
       <c r="E6">
-        <v>1.63222527052263</v>
+        <v>1.270342024125088</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -589,19 +598,19 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>2.397891963109359</v>
+        <v>2.427440633245382</v>
       </c>
       <c r="E7">
-        <v>1.631399086505698</v>
+        <v>1.627971341250459</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -612,19 +621,19 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>2.285714285714292</v>
+        <v>1.879989698686586</v>
       </c>
       <c r="E8">
-        <v>1.894546052252768</v>
+        <v>1.69400909621784</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -635,19 +644,19 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>7.173678532901825</v>
+        <v>7.194826192400974</v>
       </c>
       <c r="E9">
-        <v>8.100876252980063</v>
+        <v>8.144108148430959</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -658,19 +667,19 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D10">
-        <v>0.1082837033026536</v>
+        <v>-0.326086956521749</v>
       </c>
       <c r="E10">
-        <v>-1.494981145138496</v>
+        <v>-2.0247623622764</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -681,19 +690,19 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D11">
-        <v>-1.440922186651328</v>
+        <v>-1.72043010752688</v>
       </c>
       <c r="E11">
-        <v>-2.963354149741118</v>
+        <v>-3.106185546449092</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -704,19 +713,19 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D12">
-        <v>-46.50877909350755</v>
+        <v>-46.36916835699796</v>
       </c>
       <c r="E12">
-        <v>-55.59266721589984</v>
+        <v>-55.34545963085596</v>
       </c>
       <c r="F12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -727,88 +736,88 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D13">
-        <v>0.5161640858462349</v>
+        <v>0.4907306434024008</v>
       </c>
       <c r="E13">
-        <v>-1.153267653173353</v>
+        <v>-1.270485350847637</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D14">
-        <v>4.35020519835841</v>
+        <v>-1.235245676640133</v>
       </c>
       <c r="E14">
-        <v>4.35020519835841</v>
+        <v>-3.167965518428194</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D15">
-        <v>10.7103825136612</v>
+        <v>-7.344940152339497</v>
       </c>
       <c r="E15">
-        <v>10.7103825136612</v>
+        <v>-8.894539561067987</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D16">
-        <v>3.022198448783094</v>
+        <v>3.6727879799666</v>
       </c>
       <c r="E16">
-        <v>3.022198448783094</v>
+        <v>3.60132249582002</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -816,22 +825,22 @@
         <v>2010</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D17">
-        <v>9.290187891440489</v>
+        <v>4.818949087939018</v>
       </c>
       <c r="E17">
-        <v>9.290187891440489</v>
+        <v>4.818949087939018</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -839,22 +848,22 @@
         <v>2010</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D18">
-        <v>2.024922118380061</v>
+        <v>11.29866594064797</v>
       </c>
       <c r="E18">
-        <v>2.024922118380061</v>
+        <v>11.29866594064797</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -862,22 +871,22 @@
         <v>2010</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D19">
-        <v>2.397891963109359</v>
+        <v>2.402562733582492</v>
       </c>
       <c r="E19">
-        <v>2.397891963109359</v>
+        <v>2.402562733582492</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -885,22 +894,22 @@
         <v>2010</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D20">
-        <v>2.285714285714292</v>
+        <v>8.84210526315789</v>
       </c>
       <c r="E20">
-        <v>2.285714285714292</v>
+        <v>8.84210526315789</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -908,22 +917,22 @@
         <v>2010</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D21">
-        <v>7.173678532901825</v>
+        <v>1.604554865424426</v>
       </c>
       <c r="E21">
-        <v>7.173678532901825</v>
+        <v>1.604554865424426</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -931,22 +940,22 @@
         <v>2010</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D22">
-        <v>0.1082837033026536</v>
+        <v>2.427440633245382</v>
       </c>
       <c r="E22">
-        <v>0.1082837033026536</v>
+        <v>2.427440633245382</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -954,22 +963,22 @@
         <v>2010</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D23">
-        <v>-1.440922186651328</v>
+        <v>1.879989698686586</v>
       </c>
       <c r="E23">
-        <v>-1.440922186651328</v>
+        <v>1.879989698686586</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -977,22 +986,22 @@
         <v>2010</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D24">
-        <v>-46.50877909350755</v>
+        <v>7.194826192400974</v>
       </c>
       <c r="E24">
-        <v>-46.50877909350755</v>
+        <v>7.194826192400974</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G24" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1000,160 +1009,160 @@
         <v>2010</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D25">
-        <v>0.5161640858462349</v>
+        <v>-0.326086956521749</v>
       </c>
       <c r="E25">
-        <v>0.5161640858462349</v>
+        <v>-0.326086956521749</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G25" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D26">
-        <v>4.35020519835841</v>
+        <v>-1.72043010752688</v>
       </c>
       <c r="E26">
-        <v>0.5875832206046367</v>
+        <v>-1.72043010752688</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D27">
-        <v>10.7103825136612</v>
+        <v>-46.36916835699796</v>
       </c>
       <c r="E27">
-        <v>8.436316795270802</v>
+        <v>-46.36916835699796</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="B28" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D28">
-        <v>3.022198448783094</v>
+        <v>0.4907306434024008</v>
       </c>
       <c r="E28">
-        <v>5.171540530193047</v>
+        <v>0.4907306434024008</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D29">
-        <v>9.290187891440489</v>
+        <v>-1.235245676640133</v>
       </c>
       <c r="E29">
-        <v>14.24665463795645</v>
+        <v>-1.235245676640133</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G29" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D30">
-        <v>2.024922118380061</v>
+        <v>-7.344940152339497</v>
       </c>
       <c r="E30">
-        <v>0.743526186134849</v>
+        <v>-7.344940152339497</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G30" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D31">
-        <v>2.397891963109359</v>
+        <v>3.6727879799666</v>
       </c>
       <c r="E31">
-        <v>0.3319917866220674</v>
+        <v>3.6727879799666</v>
       </c>
       <c r="F31" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G31" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1161,22 +1170,22 @@
         <v>2014</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D32">
-        <v>2.285714285714292</v>
+        <v>4.818949087939018</v>
       </c>
       <c r="E32">
-        <v>1.031802567985925</v>
+        <v>1.434321076380486</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G32" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1184,22 +1193,22 @@
         <v>2014</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D33">
-        <v>7.173678532901825</v>
+        <v>11.29866594064797</v>
       </c>
       <c r="E33">
-        <v>9.773277512312969</v>
+        <v>9.353059737108191</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G33" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1207,22 +1216,22 @@
         <v>2014</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D34">
-        <v>0.1082837033026536</v>
+        <v>2.402562733582492</v>
       </c>
       <c r="E34">
-        <v>-4.002949436234216</v>
+        <v>4.520810184903002</v>
       </c>
       <c r="F34" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G34" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1230,22 +1239,22 @@
         <v>2014</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D35">
-        <v>-1.440922186651328</v>
+        <v>8.84210526315789</v>
       </c>
       <c r="E35">
-        <v>-5.062926210462702</v>
+        <v>13.21213717449071</v>
       </c>
       <c r="F35" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G35" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1253,22 +1262,22 @@
         <v>2014</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D36">
-        <v>-46.50877909350755</v>
+        <v>1.604554865424426</v>
       </c>
       <c r="E36">
-        <v>-56.62306739616567</v>
+        <v>0.4123999444396333</v>
       </c>
       <c r="F36" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G36" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1276,229 +1285,229 @@
         <v>2014</v>
       </c>
       <c r="B37" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D37">
-        <v>0.5161640858462349</v>
+        <v>2.427440633245382</v>
       </c>
       <c r="E37">
-        <v>-3.702299542820164</v>
+        <v>0.2920207462628057</v>
       </c>
       <c r="F37" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G37" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B38" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D38">
-        <v>4.35020519835841</v>
+        <v>1.879989698686586</v>
       </c>
       <c r="E38">
-        <v>3.383283553602231</v>
+        <v>1.038114862607362</v>
       </c>
       <c r="F38" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G38" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B39" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D39">
-        <v>10.7103825136612</v>
+        <v>7.194826192400974</v>
       </c>
       <c r="E39">
-        <v>9.978341861521631</v>
+        <v>9.844770809263956</v>
       </c>
       <c r="F39" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G39" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D40">
-        <v>3.022198448783094</v>
+        <v>-0.326086956521749</v>
       </c>
       <c r="E40">
-        <v>4.975592679252363</v>
+        <v>-4.583492978506826</v>
       </c>
       <c r="F40" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G40" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B41" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D41">
-        <v>9.290187891440489</v>
+        <v>-1.72043010752688</v>
       </c>
       <c r="E41">
-        <v>12.08567593496913</v>
+        <v>-4.98047577053488</v>
       </c>
       <c r="F41" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G41" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D42">
-        <v>2.024922118380061</v>
+        <v>-46.36916835699796</v>
       </c>
       <c r="E42">
-        <v>2.350626952871099</v>
+        <v>-56.27891424570422</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G42" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D43">
-        <v>2.397891963109359</v>
+        <v>0.4907306434024008</v>
       </c>
       <c r="E43">
-        <v>2.340149683490385</v>
+        <v>-3.931194229231569</v>
       </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G43" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C44" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D44">
-        <v>2.285714285714292</v>
+        <v>-1.235245676640133</v>
       </c>
       <c r="E44">
-        <v>2.605762487767027</v>
+        <v>-5.802208995548391</v>
       </c>
       <c r="F44" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G44" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B45" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D45">
-        <v>7.173678532901825</v>
+        <v>-7.344940152339497</v>
       </c>
       <c r="E45">
-        <v>9.042832571887942</v>
+        <v>-9.706545577811344</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G45" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D46">
-        <v>0.1082837033026536</v>
+        <v>3.6727879799666</v>
       </c>
       <c r="E46">
-        <v>-0.7217798163800426</v>
+        <v>3.760238288587101</v>
       </c>
       <c r="F46" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G46" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1506,22 +1515,22 @@
         <v>2018</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C47" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D47">
-        <v>-1.440922186651328</v>
+        <v>4.818949087939018</v>
       </c>
       <c r="E47">
-        <v>-2.071216292825427</v>
+        <v>3.955675435843912</v>
       </c>
       <c r="F47" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G47" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1529,22 +1538,22 @@
         <v>2018</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D48">
-        <v>-46.50877909350755</v>
+        <v>11.29866594064797</v>
       </c>
       <c r="E48">
-        <v>-51.05705150122986</v>
+        <v>10.63937071277274</v>
       </c>
       <c r="F48" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G48" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1552,298 +1561,643 @@
         <v>2018</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D49">
-        <v>0.5161640858462349</v>
+        <v>2.402562733582492</v>
       </c>
       <c r="E49">
-        <v>-0.3911901551618415</v>
+        <v>4.349078924732492</v>
       </c>
       <c r="F49" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G49" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D50">
-        <v>4.35020519835841</v>
+        <v>8.84210526315789</v>
       </c>
       <c r="E50">
-        <v>-0.8514681264693413</v>
+        <v>11.36572386845493</v>
       </c>
       <c r="F50" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G50" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B51" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D51">
-        <v>10.7103825136612</v>
+        <v>1.604554865424426</v>
       </c>
       <c r="E51">
-        <v>7.772537436199933</v>
+        <v>1.964320154153819</v>
       </c>
       <c r="F51" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G51" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B52" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D52">
-        <v>3.022198448783094</v>
+        <v>2.427440633245382</v>
       </c>
       <c r="E52">
-        <v>2.475588634409105</v>
+        <v>2.300058852257826</v>
       </c>
       <c r="F52" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G52" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B53" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D53">
-        <v>9.290187891440489</v>
+        <v>1.879989698686586</v>
       </c>
       <c r="E53">
-        <v>12.09768926023513</v>
+        <v>2.380154888649418</v>
       </c>
       <c r="F53" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G53" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C54" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D54">
-        <v>2.024922118380061</v>
+        <v>7.194826192400974</v>
       </c>
       <c r="E54">
-        <v>-1.468962141794489</v>
+        <v>9.049541256638125</v>
       </c>
       <c r="F54" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G54" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B55" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C55" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D55">
-        <v>2.397891963109359</v>
+        <v>-0.326086956521749</v>
       </c>
       <c r="E55">
-        <v>-1.693838513232154</v>
+        <v>-1.258052860365325</v>
       </c>
       <c r="F55" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G55" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C56" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D56">
-        <v>2.285714285714292</v>
+        <v>-1.72043010752688</v>
       </c>
       <c r="E56">
-        <v>-1.143462461900912</v>
+        <v>-2.227660214988835</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G56" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B57" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D57">
-        <v>7.173678532901825</v>
+        <v>-46.36916835699796</v>
       </c>
       <c r="E57">
-        <v>7.667809386312056</v>
+        <v>-50.85717459258375</v>
       </c>
       <c r="F57" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G57" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D58">
-        <v>0.1082837033026536</v>
+        <v>0.4907306434024008</v>
       </c>
       <c r="E58">
-        <v>-6.063399526031018</v>
+        <v>-0.5434588963579809</v>
       </c>
       <c r="F58" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G58" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B59" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C59" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D59">
-        <v>-1.440922186651328</v>
+        <v>-1.235245676640133</v>
       </c>
       <c r="E59">
-        <v>-7.179077005630766</v>
+        <v>-2.327620292157987</v>
       </c>
       <c r="F59" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B60" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C60" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D60">
-        <v>-46.50877909350755</v>
+        <v>-7.344940152339497</v>
       </c>
       <c r="E60">
-        <v>-56.41044032645397</v>
+        <v>-7.562600828237558</v>
       </c>
       <c r="F60" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G60" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
+        <v>2018</v>
+      </c>
+      <c r="B61" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61">
+        <v>3.6727879799666</v>
+      </c>
+      <c r="E61">
+        <v>4.605455518747332</v>
+      </c>
+      <c r="F61" t="s">
+        <v>23</v>
+      </c>
+      <c r="G61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62">
         <v>2022</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62">
+        <v>4.818949087939018</v>
+      </c>
+      <c r="E62">
+        <v>0.008955569026754873</v>
+      </c>
+      <c r="F62" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63">
+        <v>2022</v>
+      </c>
+      <c r="B63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" t="s">
+        <v>22</v>
+      </c>
+      <c r="D63">
+        <v>11.29866594064797</v>
+      </c>
+      <c r="E63">
+        <v>8.730091189281499</v>
+      </c>
+      <c r="F63" t="s">
+        <v>23</v>
+      </c>
+      <c r="G63" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64">
+        <v>2022</v>
+      </c>
+      <c r="B64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" t="s">
+        <v>23</v>
+      </c>
+      <c r="D64">
+        <v>2.402562733582492</v>
+      </c>
+      <c r="E64">
+        <v>1.730876500872622</v>
+      </c>
+      <c r="F64" t="s">
+        <v>23</v>
+      </c>
+      <c r="G64" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65">
+        <v>2022</v>
+      </c>
+      <c r="B65" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65">
+        <v>8.84210526315789</v>
+      </c>
+      <c r="E65">
+        <v>11.08654647454055</v>
+      </c>
+      <c r="F65" t="s">
+        <v>23</v>
+      </c>
+      <c r="G65" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66">
+        <v>2022</v>
+      </c>
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>22</v>
+      </c>
+      <c r="D66">
+        <v>1.604554865424426</v>
+      </c>
+      <c r="E66">
+        <v>-1.881716478465326</v>
+      </c>
+      <c r="F66" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67">
+        <v>2022</v>
+      </c>
+      <c r="B67" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" t="s">
+        <v>22</v>
+      </c>
+      <c r="D67">
+        <v>2.427440633245382</v>
+      </c>
+      <c r="E67">
+        <v>-1.717828340340283</v>
+      </c>
+      <c r="F67" t="s">
+        <v>22</v>
+      </c>
+      <c r="G67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68">
+        <v>2022</v>
+      </c>
+      <c r="B68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" t="s">
+        <v>22</v>
+      </c>
+      <c r="D68">
+        <v>1.879989698686586</v>
+      </c>
+      <c r="E68">
+        <v>-1.268718015257621</v>
+      </c>
+      <c r="F68" t="s">
+        <v>22</v>
+      </c>
+      <c r="G68" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69">
+        <v>2022</v>
+      </c>
+      <c r="B69" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69">
+        <v>7.194826192400974</v>
+      </c>
+      <c r="E69">
+        <v>7.73452815880882</v>
+      </c>
+      <c r="F69" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70">
+        <v>2022</v>
+      </c>
+      <c r="B70" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70">
+        <v>-0.326086956521749</v>
+      </c>
+      <c r="E70">
+        <v>-6.628330995289902</v>
+      </c>
+      <c r="F70" t="s">
+        <v>22</v>
+      </c>
+      <c r="G70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71">
+        <v>2022</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="s">
+        <v>22</v>
+      </c>
+      <c r="D71">
+        <v>-1.72043010752688</v>
+      </c>
+      <c r="E71">
+        <v>-7.147327230489436</v>
+      </c>
+      <c r="F71" t="s">
+        <v>22</v>
+      </c>
+      <c r="G71" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72">
+        <v>2022</v>
+      </c>
+      <c r="B72" t="s">
+        <v>17</v>
+      </c>
+      <c r="C72" t="s">
+        <v>22</v>
+      </c>
+      <c r="D72">
+        <v>-46.36916835699796</v>
+      </c>
+      <c r="E72">
+        <v>-56.10337142360186</v>
+      </c>
+      <c r="F72" t="s">
+        <v>22</v>
+      </c>
+      <c r="G72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73">
+        <v>2022</v>
+      </c>
+      <c r="B73" t="s">
         <v>18</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C73" t="s">
+        <v>22</v>
+      </c>
+      <c r="D73">
+        <v>0.4907306434024008</v>
+      </c>
+      <c r="E73">
+        <v>-5.880209986038962</v>
+      </c>
+      <c r="F73" t="s">
+        <v>22</v>
+      </c>
+      <c r="G73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74">
+        <v>2022</v>
+      </c>
+      <c r="B74" t="s">
         <v>19</v>
       </c>
-      <c r="D61">
-        <v>0.5161640858462349</v>
-      </c>
-      <c r="E61">
-        <v>-5.680203385192162</v>
-      </c>
-      <c r="F61" t="s">
-        <v>19</v>
-      </c>
-      <c r="G61" t="s">
+      <c r="C74" t="s">
+        <v>22</v>
+      </c>
+      <c r="D74">
+        <v>-1.235245676640133</v>
+      </c>
+      <c r="E74">
+        <v>-7.771144457473818</v>
+      </c>
+      <c r="F74" t="s">
+        <v>22</v>
+      </c>
+      <c r="G74" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75">
+        <v>2022</v>
+      </c>
+      <c r="B75" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" t="s">
+        <v>22</v>
+      </c>
+      <c r="D75">
+        <v>-7.344940152339497</v>
+      </c>
+      <c r="E75">
+        <v>-11.85949981973358</v>
+      </c>
+      <c r="F75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G75" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76">
+        <v>2022</v>
+      </c>
+      <c r="B76" t="s">
         <v>21</v>
+      </c>
+      <c r="C76" t="s">
+        <v>23</v>
+      </c>
+      <c r="D76">
+        <v>3.6727879799666</v>
+      </c>
+      <c r="E76">
+        <v>1.502192302137329</v>
+      </c>
+      <c r="F76" t="s">
+        <v>23</v>
+      </c>
+      <c r="G76" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
